--- a/Dependencies/Analysis_Outputs/Ping_2018/Reporter_RAAS_byAAS_alldatasets.xlsx
+++ b/Dependencies/Analysis_Outputs/Ping_2018/Reporter_RAAS_byAAS_alldatasets.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J35"/>
+  <dimension ref="A1:J104"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -478,56 +478,40 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>P to T</t>
+          <t>F to M</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>-1.456311333003006</v>
+        <v>-1.727053549021357</v>
       </c>
       <c r="C2" t="n">
-        <v>-1.504678437542773</v>
+        <v>-2.337362811504208</v>
       </c>
       <c r="D2" t="n">
-        <v>-1.745266005724592</v>
-      </c>
-      <c r="E2" t="n">
-        <v>-1.474763984926852</v>
-      </c>
+        <v>-3.19300086721324</v>
+      </c>
+      <c r="E2" t="inlineStr"/>
       <c r="F2" t="n">
-        <v>-1.889643625234855</v>
-      </c>
-      <c r="G2" t="n">
-        <v>-1.638045256233094</v>
-      </c>
-      <c r="H2" t="n">
-        <v>-1.740292243890416</v>
-      </c>
-      <c r="I2" t="n">
-        <v>-1.849631821167082</v>
-      </c>
-      <c r="J2" t="n">
-        <v>-1.516425305642192</v>
-      </c>
+        <v>-3.829112479141449</v>
+      </c>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Q to A</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>-0.3619759289519581</v>
-      </c>
-      <c r="C3" t="n">
-        <v>-0.7644329691406446</v>
-      </c>
+          <t>Q to P</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr"/>
+      <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="n">
-        <v>0.4651104813797439</v>
-      </c>
-      <c r="F3" t="n">
-        <v>0.56939650131213</v>
-      </c>
+        <v>-0.2445810747403609</v>
+      </c>
+      <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
@@ -536,7 +520,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>T to D</t>
+          <t>T to C</t>
         </is>
       </c>
       <c r="B4" t="inlineStr"/>
@@ -546,64 +530,60 @@
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr"/>
-      <c r="I4" t="n">
-        <v>-1.712674224120059</v>
-      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="J4" t="n">
-        <v>-1.072414206849355</v>
+        <v>-3.081037614646761</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>T to G</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr"/>
+          <t>L to V</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>-1.883546273157956</v>
+      </c>
       <c r="C5" t="n">
-        <v>-0.7712412666354529</v>
+        <v>-1.810113519196862</v>
       </c>
       <c r="D5" t="n">
-        <v>-1.081242948761708</v>
+        <v>-1.269942303422608</v>
       </c>
       <c r="E5" t="n">
-        <v>-1.307376301412282</v>
+        <v>-0.1979191233709345</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.016906836931211</v>
+        <v>-3.610322374350784</v>
       </c>
       <c r="G5" t="n">
-        <v>-2.068791044590431</v>
-      </c>
-      <c r="H5" t="inlineStr"/>
+        <v>-1.902780865983694</v>
+      </c>
+      <c r="H5" t="n">
+        <v>-2.580291811097522</v>
+      </c>
       <c r="I5" t="n">
-        <v>-2.202513924562711</v>
+        <v>-2.062019001195512</v>
       </c>
       <c r="J5" t="n">
-        <v>-2.532685689256852</v>
+        <v>-1.950020643653497</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>V to L</t>
+          <t>L to P</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.27636536768703</v>
-      </c>
-      <c r="C6" t="n">
-        <v>0.1611967979390617</v>
-      </c>
+        <v>0.03979614585522858</v>
+      </c>
+      <c r="C6" t="inlineStr"/>
       <c r="D6" t="n">
-        <v>0.2032939194769821</v>
-      </c>
-      <c r="E6" t="n">
-        <v>-0.5536287464575707</v>
-      </c>
-      <c r="F6" t="n">
-        <v>-0.05897333021202279</v>
-      </c>
+        <v>-1.542421483106274</v>
+      </c>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr"/>
@@ -612,71 +592,67 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>C to G</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>-1.604583302921172</v>
-      </c>
-      <c r="C7" t="inlineStr"/>
-      <c r="D7" t="n">
-        <v>-1.650305588338055</v>
-      </c>
-      <c r="E7" t="n">
-        <v>-1.498145046900468</v>
-      </c>
-      <c r="F7" t="n">
-        <v>-1.429114256626512</v>
-      </c>
+          <t>M to E</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr"/>
+      <c r="C7" t="n">
+        <v>2.030321733369708</v>
+      </c>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr"/>
+      <c r="I7" t="n">
+        <v>-3.272603034383185</v>
+      </c>
       <c r="J7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>W to S</t>
+          <t>L to S</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-2.885578204024989</v>
+        <v>-3.328727118921855</v>
       </c>
       <c r="C8" t="n">
-        <v>-2.211757141998453</v>
+        <v>-3.41578199313019</v>
       </c>
       <c r="D8" t="n">
-        <v>-2.80182751423905</v>
+        <v>-3.448045289834815</v>
       </c>
       <c r="E8" t="n">
-        <v>-2.684605095576888</v>
+        <v>-3.736628005009043</v>
       </c>
       <c r="F8" t="n">
-        <v>-2.585448009274374</v>
+        <v>-3.602915382759653</v>
       </c>
       <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr"/>
+      <c r="H8" t="n">
+        <v>-3.215605417036939</v>
+      </c>
+      <c r="I8" t="n">
+        <v>-3.322837520547845</v>
+      </c>
       <c r="J8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>S to C</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>-1.119477822045281</v>
-      </c>
-      <c r="C9" t="n">
-        <v>-0.5428100240708476</v>
-      </c>
-      <c r="D9" t="n">
-        <v>-0.76889570955057</v>
-      </c>
-      <c r="E9" t="inlineStr"/>
+          <t>M to G</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr"/>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="n">
+        <v>-1.570972821613221</v>
+      </c>
       <c r="F9" t="n">
-        <v>-1.603796046659123</v>
+        <v>-2.073913401043293</v>
       </c>
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr"/>
@@ -686,53 +662,49 @@
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>L to V</t>
+          <t>G to Q</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>-1.390571289949965</v>
+        <v>-2.744358254712862</v>
       </c>
       <c r="C10" t="n">
-        <v>-1.683394376609969</v>
+        <v>-2.810675393222065</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.2926400842097129</v>
+        <v>-2.801736030942985</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.1979191233709345</v>
-      </c>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="n">
-        <v>-0.8184203416481879</v>
-      </c>
+        <v>-2.725378825318345</v>
+      </c>
+      <c r="F10" t="n">
+        <v>-2.678515653154976</v>
+      </c>
+      <c r="G10" t="inlineStr"/>
       <c r="H10" t="n">
-        <v>-1.286076706226269</v>
+        <v>-2.670067730457079</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.304531892037376</v>
+        <v>-2.900077726771973</v>
       </c>
       <c r="J10" t="n">
-        <v>0.6572150035971557</v>
+        <v>-2.66693287997521</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>M to V</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>-0.5067863028911419</v>
-      </c>
+          <t>M to N</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr"/>
       <c r="C11" t="n">
-        <v>-1.302905102758689</v>
-      </c>
-      <c r="D11" t="n">
-        <v>-1.466497495480635</v>
-      </c>
+        <v>0.2110591857205794</v>
+      </c>
+      <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="n">
-        <v>-1.753313564223895</v>
+        <v>-1.763359657806746</v>
       </c>
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr"/>
@@ -742,95 +714,93 @@
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>S to N</t>
+          <t>A to S</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.1607029791061756</v>
+        <v>-0.9349556938567645</v>
       </c>
       <c r="C12" t="n">
-        <v>0.9612546517883696</v>
+        <v>-0.8876119507146282</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.01792181977638689</v>
+        <v>-2.059810010622027</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.983802386303317</v>
+        <v>-1.792262090071939</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.4218760927984735</v>
+        <v>-2.041614480763192</v>
       </c>
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr"/>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
+      <c r="I12" t="n">
+        <v>-1.73284789650191</v>
+      </c>
+      <c r="J12" t="n">
+        <v>-1.842268417083817</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>T to S</t>
+          <t>L to T</t>
         </is>
       </c>
       <c r="B13" t="inlineStr"/>
-      <c r="C13" t="inlineStr"/>
-      <c r="D13" t="n">
-        <v>-2.129078199160038</v>
-      </c>
-      <c r="E13" t="n">
-        <v>-2.343313973296302</v>
-      </c>
-      <c r="F13" t="n">
-        <v>-1.772160073286773</v>
-      </c>
+      <c r="C13" t="n">
+        <v>-0.1497227903399237</v>
+      </c>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr"/>
-      <c r="I13" t="inlineStr"/>
+      <c r="I13" t="n">
+        <v>-2.420994805717631</v>
+      </c>
       <c r="J13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>G to T</t>
+          <t>M to T</t>
         </is>
       </c>
       <c r="B14" t="inlineStr"/>
-      <c r="C14" t="n">
-        <v>-2.894318537672504</v>
-      </c>
-      <c r="D14" t="n">
-        <v>-2.753593794502206</v>
-      </c>
-      <c r="E14" t="n">
-        <v>-2.69025097065938</v>
-      </c>
-      <c r="F14" t="n">
-        <v>-2.71539495085535</v>
-      </c>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr"/>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="n">
+        <v>-2.589561049762143</v>
+      </c>
+      <c r="H14" t="n">
+        <v>-2.31498668887464</v>
+      </c>
+      <c r="I14" t="n">
+        <v>-2.33260375582959</v>
+      </c>
+      <c r="J14" t="n">
+        <v>-2.300096095905567</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>Q to G</t>
+          <t>L to N</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>-1.957982223401954</v>
-      </c>
-      <c r="C15" t="n">
-        <v>-2.019897747519391</v>
-      </c>
-      <c r="D15" t="n">
-        <v>-1.733591747121958</v>
-      </c>
+        <v>-0.7460353441516747</v>
+      </c>
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" t="inlineStr"/>
       <c r="E15" t="n">
-        <v>-1.923562591910295</v>
+        <v>-3.504530029129409</v>
       </c>
       <c r="F15" t="n">
-        <v>-2.120307326445594</v>
+        <v>-0.6698574314526985</v>
       </c>
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr"/>
@@ -840,23 +810,17 @@
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>G to S</t>
-        </is>
-      </c>
-      <c r="B16" t="n">
-        <v>-2.334158556973145</v>
-      </c>
-      <c r="C16" t="n">
-        <v>-2.203794771150561</v>
-      </c>
-      <c r="D16" t="n">
-        <v>-1.677643734319848</v>
-      </c>
+          <t>H to D</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr"/>
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="inlineStr"/>
       <c r="E16" t="n">
-        <v>-1.240054774496784</v>
+        <v>-2.443042362216244</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.18231125391813</v>
+        <v>-1.861486441134107</v>
       </c>
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr"/>
@@ -866,49 +830,47 @@
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>V to P</t>
+          <t>A to G</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>-2.375410126229204</v>
+        <v>-0.5317275257810317</v>
       </c>
       <c r="C17" t="n">
-        <v>-2.53339669101649</v>
+        <v>-3.118354962056315</v>
       </c>
       <c r="D17" t="n">
-        <v>-2.430893036706252</v>
-      </c>
-      <c r="E17" t="n">
-        <v>-2.531518954683574</v>
-      </c>
+        <v>-2.893505087305775</v>
+      </c>
+      <c r="E17" t="inlineStr"/>
       <c r="F17" t="n">
-        <v>-2.820705545703728</v>
-      </c>
-      <c r="G17" t="inlineStr"/>
+        <v>-2.824286212743124</v>
+      </c>
+      <c r="G17" t="n">
+        <v>-0.5721990618838579</v>
+      </c>
       <c r="H17" t="inlineStr"/>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
+      <c r="I17" t="n">
+        <v>0.2009495404977402</v>
+      </c>
+      <c r="J17" t="n">
+        <v>-2.235370584016366</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>G to Q</t>
-        </is>
-      </c>
-      <c r="B18" t="n">
-        <v>-2.1343769909623</v>
-      </c>
-      <c r="C18" t="n">
-        <v>-2.705482115789578</v>
-      </c>
+          <t>C to N</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr"/>
+      <c r="C18" t="inlineStr"/>
       <c r="D18" t="n">
-        <v>-2.60800824219249</v>
-      </c>
-      <c r="E18" t="n">
-        <v>-2.686182054211174</v>
-      </c>
+        <v>-0.4110620493613065</v>
+      </c>
+      <c r="E18" t="inlineStr"/>
       <c r="F18" t="n">
-        <v>-2.505686495639354</v>
+        <v>-0.008201275101517247</v>
       </c>
       <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr"/>
@@ -918,23 +880,21 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>A to T</t>
+          <t>P to Q</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>-0.05086751400848828</v>
-      </c>
-      <c r="C19" t="n">
-        <v>-1.200784735436127</v>
-      </c>
+        <v>0.5585032223250124</v>
+      </c>
+      <c r="C19" t="inlineStr"/>
       <c r="D19" t="n">
-        <v>-1.475315576216427</v>
+        <v>-2.861876588317117</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.06838000895293216</v>
+        <v>0.06534429501985639</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.1833849812189074</v>
+        <v>-3.125569234887854</v>
       </c>
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr"/>
@@ -944,151 +904,147 @@
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>A to V</t>
-        </is>
-      </c>
-      <c r="B20" t="n">
-        <v>-0.607017545426637</v>
-      </c>
-      <c r="C20" t="n">
-        <v>-0.2994875813223888</v>
-      </c>
+          <t>G to N</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr"/>
+      <c r="C20" t="inlineStr"/>
       <c r="D20" t="n">
-        <v>-0.2358350772062613</v>
-      </c>
-      <c r="E20" t="n">
-        <v>-0.2492998169569994</v>
-      </c>
-      <c r="F20" t="n">
-        <v>-0.3890156441501045</v>
-      </c>
+        <v>-2.767319136895065</v>
+      </c>
+      <c r="E20" t="inlineStr"/>
+      <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr"/>
       <c r="H20" t="n">
-        <v>-1.187371363352375</v>
+        <v>-2.518471507692384</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.09783632915559025</v>
-      </c>
-      <c r="J20" t="n">
-        <v>-0.6648284746504712</v>
-      </c>
+        <v>-1.750393873539942</v>
+      </c>
+      <c r="J20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>P to A</t>
+          <t>M to D</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>-1.856120487238615</v>
+        <v>-2.909256036032624</v>
       </c>
       <c r="C21" t="n">
-        <v>-0.8806815241504841</v>
+        <v>-2.417698931441598</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.059605036181766</v>
+        <v>-3.001783776668217</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.897554866263773</v>
+        <v>-0.03004848904649286</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.1912597211782233</v>
+        <v>-3.034320143655385</v>
       </c>
       <c r="G21" t="inlineStr"/>
-      <c r="H21" t="inlineStr"/>
-      <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
+      <c r="H21" t="n">
+        <v>-1.433926206749332</v>
+      </c>
+      <c r="I21" t="n">
+        <v>-3.019556902082101</v>
+      </c>
+      <c r="J21" t="n">
+        <v>-3.027832779888084</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>G to E</t>
+          <t>S to G</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>-1.271150186497037</v>
-      </c>
-      <c r="C22" t="inlineStr"/>
+        <v>-2.868413795260239</v>
+      </c>
+      <c r="C22" t="n">
+        <v>-1.917506085911143</v>
+      </c>
       <c r="D22" t="n">
-        <v>-1.943874142887593</v>
+        <v>-0.657589109992647</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.409815740804866</v>
+        <v>-1.706884685566994</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.64652636017601</v>
-      </c>
-      <c r="G22" t="inlineStr"/>
+        <v>-2.629822411214032</v>
+      </c>
+      <c r="G22" t="n">
+        <v>-0.946960170181026</v>
+      </c>
       <c r="H22" t="inlineStr"/>
       <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
+      <c r="J22" t="n">
+        <v>-3.125443727544346</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>A to P</t>
-        </is>
-      </c>
-      <c r="B23" t="n">
-        <v>-2.709267638635628</v>
-      </c>
-      <c r="C23" t="n">
-        <v>-1.641646736359874</v>
-      </c>
-      <c r="D23" t="n">
-        <v>-2.630086340349047</v>
-      </c>
-      <c r="E23" t="n">
-        <v>-2.164443650368841</v>
-      </c>
+          <t>T to L</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr"/>
+      <c r="C23" t="inlineStr"/>
+      <c r="D23" t="inlineStr"/>
+      <c r="E23" t="inlineStr"/>
       <c r="F23" t="n">
-        <v>-2.055055819065081</v>
+        <v>1.664864551160061</v>
       </c>
       <c r="G23" t="inlineStr"/>
       <c r="H23" t="inlineStr"/>
-      <c r="I23" t="inlineStr"/>
+      <c r="I23" t="n">
+        <v>1.945140599196265</v>
+      </c>
       <c r="J23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>S to G</t>
+          <t>S to C</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>-2.61569073890176</v>
-      </c>
-      <c r="C24" t="inlineStr"/>
+        <v>-2.637903257910638</v>
+      </c>
+      <c r="C24" t="n">
+        <v>-0.5428100240708476</v>
+      </c>
       <c r="D24" t="n">
-        <v>-0.6459388420335168</v>
+        <v>-0.76889570955057</v>
       </c>
       <c r="E24" t="n">
-        <v>-1.706884685566994</v>
+        <v>-0.9980608897109512</v>
       </c>
       <c r="F24" t="n">
-        <v>-2.151714281315133</v>
+        <v>0.1052649444633963</v>
       </c>
       <c r="G24" t="inlineStr"/>
       <c r="H24" t="inlineStr"/>
-      <c r="I24" t="inlineStr"/>
+      <c r="I24" t="n">
+        <v>-1.6969413362056</v>
+      </c>
       <c r="J24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>Q to S</t>
-        </is>
-      </c>
-      <c r="B25" t="n">
-        <v>-1.23279626936226</v>
-      </c>
+          <t>P to L</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr"/>
       <c r="C25" t="inlineStr"/>
-      <c r="D25" t="n">
-        <v>-1.445684801436449</v>
-      </c>
+      <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr"/>
       <c r="F25" t="n">
-        <v>-1.106924249194905</v>
+        <v>-0.1475214355638222</v>
       </c>
       <c r="G25" t="inlineStr"/>
       <c r="H25" t="inlineStr"/>
@@ -1098,71 +1054,91 @@
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>N to S</t>
+          <t>S to N</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>-1.123738174538168</v>
+        <v>-1.914713117250956</v>
       </c>
       <c r="C26" t="n">
-        <v>-1.73859985249358</v>
+        <v>-0.3069182152071708</v>
       </c>
       <c r="D26" t="n">
-        <v>-1.767355338190012</v>
+        <v>-2.395145001185681</v>
       </c>
       <c r="E26" t="n">
-        <v>0.01167710787669091</v>
+        <v>-0.6202857313268795</v>
       </c>
       <c r="F26" t="n">
-        <v>-1.394038801954014</v>
-      </c>
-      <c r="G26" t="inlineStr"/>
-      <c r="H26" t="inlineStr"/>
-      <c r="I26" t="inlineStr"/>
+        <v>-0.4218760927984735</v>
+      </c>
+      <c r="G26" t="n">
+        <v>-1.223043119639571</v>
+      </c>
+      <c r="H26" t="n">
+        <v>-2.534677384862027</v>
+      </c>
+      <c r="I26" t="n">
+        <v>-1.92635476990783</v>
+      </c>
       <c r="J26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>A to S</t>
+          <t>N to M</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>-1.995419646293807</v>
-      </c>
-      <c r="C27" t="inlineStr"/>
+        <v>-1.761957140688036</v>
+      </c>
+      <c r="C27" t="n">
+        <v>-2.070995853474632</v>
+      </c>
       <c r="D27" t="n">
-        <v>-1.854201366484312</v>
+        <v>-1.534163351329944</v>
       </c>
       <c r="E27" t="n">
-        <v>-1.965293719892033</v>
-      </c>
-      <c r="F27" t="inlineStr"/>
-      <c r="G27" t="inlineStr"/>
-      <c r="H27" t="inlineStr"/>
-      <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
+        <v>-2.205800752095683</v>
+      </c>
+      <c r="F27" t="n">
+        <v>-1.795935049299858</v>
+      </c>
+      <c r="G27" t="n">
+        <v>-1.608038727049597</v>
+      </c>
+      <c r="H27" t="n">
+        <v>-1.806314428838891</v>
+      </c>
+      <c r="I27" t="n">
+        <v>-1.70893194873642</v>
+      </c>
+      <c r="J27" t="n">
+        <v>-2.057071950941356</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>E to D</t>
-        </is>
-      </c>
-      <c r="B28" t="n">
-        <v>-0.3297413976630495</v>
-      </c>
+          <t>D to M</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr"/>
       <c r="C28" t="n">
-        <v>-0.2674458955549505</v>
+        <v>-3.013542340993861</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.3071172001293684</v>
-      </c>
-      <c r="E28" t="inlineStr"/>
+        <v>-0.2490899126848949</v>
+      </c>
+      <c r="E28" t="n">
+        <v>-1.722089422603733</v>
+      </c>
       <c r="F28" t="n">
-        <v>-0.3294074970866584</v>
-      </c>
-      <c r="G28" t="inlineStr"/>
+        <v>-0.8809561993602784</v>
+      </c>
+      <c r="G28" t="n">
+        <v>-3.302763202860881</v>
+      </c>
       <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr"/>
@@ -1170,184 +1146,1838 @@
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>N to G</t>
+          <t>A to T</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.2340837774220369</v>
+        <v>-0.05086751400848828</v>
       </c>
       <c r="C29" t="n">
-        <v>0.5786760043996511</v>
+        <v>-1.20564833726134</v>
       </c>
       <c r="D29" t="n">
-        <v>0.210235713523739</v>
+        <v>-1.553641157563922</v>
       </c>
       <c r="E29" t="n">
-        <v>0.7923608200848131</v>
-      </c>
-      <c r="F29" t="inlineStr"/>
+        <v>-0.3855319310917782</v>
+      </c>
+      <c r="F29" t="n">
+        <v>-0.1182077753621543</v>
+      </c>
       <c r="G29" t="inlineStr"/>
-      <c r="H29" t="inlineStr"/>
-      <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
+      <c r="H29" t="n">
+        <v>-1.758997908037059</v>
+      </c>
+      <c r="I29" t="n">
+        <v>-0.7972226805507401</v>
+      </c>
+      <c r="J29" t="n">
+        <v>-1.601737758076938</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>A to D</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr"/>
-      <c r="C30" t="inlineStr"/>
-      <c r="D30" t="inlineStr"/>
-      <c r="E30" t="inlineStr"/>
-      <c r="F30" t="inlineStr"/>
+          <t>V to A</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>-0.2745581453459159</v>
+      </c>
+      <c r="C30" t="n">
+        <v>0.01355251416744737</v>
+      </c>
+      <c r="D30" t="n">
+        <v>1.028950828059993</v>
+      </c>
+      <c r="E30" t="n">
+        <v>-1.858940607856459</v>
+      </c>
+      <c r="F30" t="n">
+        <v>-1.456868141139595</v>
+      </c>
       <c r="G30" t="n">
-        <v>-0.5675568401214499</v>
+        <v>-0.149095892234201</v>
       </c>
       <c r="H30" t="n">
-        <v>-1.235863259318905</v>
-      </c>
-      <c r="I30" t="inlineStr"/>
+        <v>-0.9057419582748181</v>
+      </c>
+      <c r="I30" t="n">
+        <v>-1.538018935605964</v>
+      </c>
       <c r="J30" t="n">
-        <v>0.2961007189974759</v>
+        <v>-0.5691518850356411</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>T to A</t>
-        </is>
-      </c>
-      <c r="B31" t="n">
-        <v>0.615813043047124</v>
-      </c>
-      <c r="C31" t="n">
-        <v>-0.6946282671818713</v>
-      </c>
+          <t>Y to F</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr"/>
+      <c r="C31" t="inlineStr"/>
       <c r="D31" t="n">
-        <v>-0.5889423499138984</v>
-      </c>
-      <c r="E31" t="n">
-        <v>0.06004564548430654</v>
-      </c>
-      <c r="F31" t="n">
-        <v>-0.4433521380929256</v>
-      </c>
-      <c r="G31" t="n">
-        <v>-0.3524515858538331</v>
-      </c>
-      <c r="H31" t="n">
-        <v>-0.6462654308030513</v>
-      </c>
+        <v>-0.5020483128568298</v>
+      </c>
+      <c r="E31" t="inlineStr"/>
+      <c r="F31" t="inlineStr"/>
+      <c r="G31" t="inlineStr"/>
+      <c r="H31" t="inlineStr"/>
       <c r="I31" t="n">
-        <v>-0.04125327046033402</v>
-      </c>
-      <c r="J31" t="n">
-        <v>-0.5825769401228599</v>
-      </c>
+        <v>0.3261091849769672</v>
+      </c>
+      <c r="J31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>V to A</t>
+          <t>W to S</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-0.1844647510121614</v>
-      </c>
-      <c r="C32" t="inlineStr"/>
+        <v>-2.856930825443489</v>
+      </c>
+      <c r="C32" t="n">
+        <v>-2.228479310013069</v>
+      </c>
       <c r="D32" t="n">
-        <v>1.028950828059993</v>
+        <v>-2.663094265351174</v>
       </c>
       <c r="E32" t="n">
-        <v>-1.858940607856459</v>
+        <v>-2.655967024023024</v>
       </c>
       <c r="F32" t="n">
-        <v>-1.447261522434069</v>
+        <v>-2.790831880921155</v>
       </c>
       <c r="G32" t="n">
-        <v>-0.149095892234201</v>
-      </c>
-      <c r="H32" t="n">
-        <v>-1.307848777181519</v>
-      </c>
-      <c r="I32" t="inlineStr"/>
-      <c r="J32" t="n">
-        <v>-0.1464116574913177</v>
-      </c>
+        <v>-2.590242462258323</v>
+      </c>
+      <c r="H32" t="inlineStr"/>
+      <c r="I32" t="n">
+        <v>-2.186017920995424</v>
+      </c>
+      <c r="J32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>N to M</t>
+          <t>N to S</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-1.149762572984605</v>
+        <v>-1.282333511272757</v>
       </c>
       <c r="C33" t="n">
-        <v>-0.914914400728583</v>
+        <v>-1.73670260354587</v>
       </c>
       <c r="D33" t="n">
-        <v>-1.911888280172409</v>
-      </c>
-      <c r="E33" t="inlineStr"/>
-      <c r="F33" t="inlineStr"/>
-      <c r="G33" t="inlineStr"/>
+        <v>-1.944229406597202</v>
+      </c>
+      <c r="E33" t="n">
+        <v>-1.453024188716823</v>
+      </c>
+      <c r="F33" t="n">
+        <v>-1.394038801954014</v>
+      </c>
+      <c r="G33" t="n">
+        <v>0.1255901563013556</v>
+      </c>
       <c r="H33" t="inlineStr"/>
-      <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
+      <c r="I33" t="n">
+        <v>-1.491778568209886</v>
+      </c>
+      <c r="J33" t="n">
+        <v>-0.7870793222696624</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>W to D</t>
-        </is>
-      </c>
-      <c r="B34" t="n">
-        <v>-2.729329311305865</v>
-      </c>
-      <c r="C34" t="n">
-        <v>-2.872319160612242</v>
-      </c>
+          <t>P to S</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr"/>
+      <c r="C34" t="inlineStr"/>
       <c r="D34" t="n">
-        <v>-2.893650219054222</v>
-      </c>
-      <c r="E34" t="n">
-        <v>-3.297109714929607</v>
-      </c>
+        <v>0.1979298271604511</v>
+      </c>
+      <c r="E34" t="inlineStr"/>
       <c r="F34" t="n">
-        <v>-3.030607253361953</v>
+        <v>-1.206443306271576</v>
       </c>
       <c r="G34" t="inlineStr"/>
-      <c r="H34" t="inlineStr"/>
-      <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
+      <c r="H34" t="n">
+        <v>-0.5906374679098432</v>
+      </c>
+      <c r="I34" t="n">
+        <v>-0.9020287742158601</v>
+      </c>
+      <c r="J34" t="n">
+        <v>-0.8861027267465595</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>L to S</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr"/>
-      <c r="C35" t="n">
-        <v>-3.41578199313019</v>
-      </c>
+          <t>M to L</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>1.047883985096965</v>
+      </c>
+      <c r="C35" t="inlineStr"/>
       <c r="D35" t="n">
-        <v>-3.428072165218711</v>
-      </c>
-      <c r="E35" t="n">
-        <v>-3.690198789098522</v>
-      </c>
+        <v>-0.08440509815701522</v>
+      </c>
+      <c r="E35" t="inlineStr"/>
       <c r="F35" t="n">
-        <v>-3.534326915613317</v>
+        <v>0.01961211254722645</v>
       </c>
       <c r="G35" t="inlineStr"/>
       <c r="H35" t="inlineStr"/>
-      <c r="I35" t="inlineStr"/>
+      <c r="I35" t="n">
+        <v>0.389827224949698</v>
+      </c>
       <c r="J35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="1" t="inlineStr">
+        <is>
+          <t>F to L</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr"/>
+      <c r="C36" t="inlineStr"/>
+      <c r="D36" t="n">
+        <v>-0.6931779928447728</v>
+      </c>
+      <c r="E36" t="n">
+        <v>-1.114367768580391</v>
+      </c>
+      <c r="F36" t="n">
+        <v>-1.32118480105795</v>
+      </c>
+      <c r="G36" t="inlineStr"/>
+      <c r="H36" t="inlineStr"/>
+      <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="1" t="inlineStr">
+        <is>
+          <t>C to V</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr"/>
+      <c r="C37" t="inlineStr"/>
+      <c r="D37" t="inlineStr"/>
+      <c r="E37" t="n">
+        <v>-3.21366070463322</v>
+      </c>
+      <c r="F37" t="inlineStr"/>
+      <c r="G37" t="inlineStr"/>
+      <c r="H37" t="inlineStr"/>
+      <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="1" t="inlineStr">
+        <is>
+          <t>E to C</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr"/>
+      <c r="C38" t="n">
+        <v>-2.561477354928849</v>
+      </c>
+      <c r="D38" t="inlineStr"/>
+      <c r="E38" t="inlineStr"/>
+      <c r="F38" t="inlineStr"/>
+      <c r="G38" t="inlineStr"/>
+      <c r="H38" t="inlineStr"/>
+      <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="1" t="inlineStr">
+        <is>
+          <t>A to M</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr"/>
+      <c r="C39" t="inlineStr"/>
+      <c r="D39" t="inlineStr"/>
+      <c r="E39" t="inlineStr"/>
+      <c r="F39" t="n">
+        <v>-3.212692997436017</v>
+      </c>
+      <c r="G39" t="inlineStr"/>
+      <c r="H39" t="inlineStr"/>
+      <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="1" t="inlineStr">
+        <is>
+          <t>Y to M</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr"/>
+      <c r="C40" t="n">
+        <v>-2.876497755127201</v>
+      </c>
+      <c r="D40" t="n">
+        <v>-2.292592506915877</v>
+      </c>
+      <c r="E40" t="inlineStr"/>
+      <c r="F40" t="inlineStr"/>
+      <c r="G40" t="inlineStr"/>
+      <c r="H40" t="inlineStr"/>
+      <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="1" t="inlineStr">
+        <is>
+          <t>N to G</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>0.2340837774220369</v>
+      </c>
+      <c r="C41" t="n">
+        <v>0.5786760043996511</v>
+      </c>
+      <c r="D41" t="n">
+        <v>0.210235713523739</v>
+      </c>
+      <c r="E41" t="n">
+        <v>0.7923608200848131</v>
+      </c>
+      <c r="F41" t="n">
+        <v>-2.272992030533022</v>
+      </c>
+      <c r="G41" t="inlineStr"/>
+      <c r="H41" t="n">
+        <v>0.6488537711892433</v>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="J41" t="n">
+        <v>0.2342352875753822</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="1" t="inlineStr">
+        <is>
+          <t>M to V</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>-0.1321391499786781</v>
+      </c>
+      <c r="C42" t="n">
+        <v>-1.302905102758689</v>
+      </c>
+      <c r="D42" t="n">
+        <v>-1.466497495480635</v>
+      </c>
+      <c r="E42" t="inlineStr"/>
+      <c r="F42" t="n">
+        <v>-1.753313564223895</v>
+      </c>
+      <c r="G42" t="inlineStr"/>
+      <c r="H42" t="inlineStr"/>
+      <c r="I42" t="n">
+        <v>-0.1590736519854822</v>
+      </c>
+      <c r="J42" t="n">
+        <v>-0.7023639794756118</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="1" t="inlineStr">
+        <is>
+          <t>Q to V</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>1.28552049360749</v>
+      </c>
+      <c r="C43" t="inlineStr"/>
+      <c r="D43" t="inlineStr"/>
+      <c r="E43" t="inlineStr"/>
+      <c r="F43" t="n">
+        <v>2.000873105475007</v>
+      </c>
+      <c r="G43" t="inlineStr"/>
+      <c r="H43" t="inlineStr"/>
+      <c r="I43" t="n">
+        <v>1.69023724741235</v>
+      </c>
+      <c r="J43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="1" t="inlineStr">
+        <is>
+          <t>V to M</t>
+        </is>
+      </c>
+      <c r="B44" t="n">
+        <v>-2.302315465005946</v>
+      </c>
+      <c r="C44" t="n">
+        <v>-0.1925567787549581</v>
+      </c>
+      <c r="D44" t="inlineStr"/>
+      <c r="E44" t="inlineStr"/>
+      <c r="F44" t="n">
+        <v>-1.021089006881581</v>
+      </c>
+      <c r="G44" t="n">
+        <v>-0.8551907018141547</v>
+      </c>
+      <c r="H44" t="inlineStr"/>
+      <c r="I44" t="n">
+        <v>-1.197381770436404</v>
+      </c>
+      <c r="J44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="1" t="inlineStr">
+        <is>
+          <t>M to F</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr"/>
+      <c r="C45" t="inlineStr"/>
+      <c r="D45" t="inlineStr"/>
+      <c r="E45" t="inlineStr"/>
+      <c r="F45" t="n">
+        <v>-2.18038339591255</v>
+      </c>
+      <c r="G45" t="inlineStr"/>
+      <c r="H45" t="inlineStr"/>
+      <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="1" t="inlineStr">
+        <is>
+          <t>P to T</t>
+        </is>
+      </c>
+      <c r="B46" t="n">
+        <v>-1.485556034428437</v>
+      </c>
+      <c r="C46" t="n">
+        <v>-1.450533528122251</v>
+      </c>
+      <c r="D46" t="n">
+        <v>-1.737235281985405</v>
+      </c>
+      <c r="E46" t="n">
+        <v>-1.478336975867874</v>
+      </c>
+      <c r="F46" t="n">
+        <v>-1.830728519312377</v>
+      </c>
+      <c r="G46" t="n">
+        <v>-1.32778027146233</v>
+      </c>
+      <c r="H46" t="n">
+        <v>-1.379445615366622</v>
+      </c>
+      <c r="I46" t="n">
+        <v>-1.708736383740888</v>
+      </c>
+      <c r="J46" t="n">
+        <v>-1.206607845553197</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="1" t="inlineStr">
+        <is>
+          <t>T to G</t>
+        </is>
+      </c>
+      <c r="B47" t="n">
+        <v>-3.16998041941182</v>
+      </c>
+      <c r="C47" t="n">
+        <v>-2.760315175782641</v>
+      </c>
+      <c r="D47" t="n">
+        <v>-3.27226844244027</v>
+      </c>
+      <c r="E47" t="n">
+        <v>-1.307376301412282</v>
+      </c>
+      <c r="F47" t="n">
+        <v>-0.9492250207473596</v>
+      </c>
+      <c r="G47" t="n">
+        <v>-2.068791044590431</v>
+      </c>
+      <c r="H47" t="n">
+        <v>-3.001865475838236</v>
+      </c>
+      <c r="I47" t="n">
+        <v>-1.583300397821857</v>
+      </c>
+      <c r="J47" t="n">
+        <v>-2.532685689256852</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="1" t="inlineStr">
+        <is>
+          <t>A to Q</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr"/>
+      <c r="C48" t="n">
+        <v>0.4378021921220056</v>
+      </c>
+      <c r="D48" t="inlineStr"/>
+      <c r="E48" t="n">
+        <v>-2.274952460175861</v>
+      </c>
+      <c r="F48" t="inlineStr"/>
+      <c r="G48" t="inlineStr"/>
+      <c r="H48" t="n">
+        <v>-1.229211128800908</v>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="J48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="1" t="inlineStr">
+        <is>
+          <t>N to T</t>
+        </is>
+      </c>
+      <c r="B49" t="n">
+        <v>1.58925791897104</v>
+      </c>
+      <c r="C49" t="inlineStr"/>
+      <c r="D49" t="inlineStr"/>
+      <c r="E49" t="inlineStr"/>
+      <c r="F49" t="inlineStr"/>
+      <c r="G49" t="inlineStr"/>
+      <c r="H49" t="inlineStr"/>
+      <c r="I49" t="inlineStr"/>
+      <c r="J49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="1" t="inlineStr">
+        <is>
+          <t>Q to A</t>
+        </is>
+      </c>
+      <c r="B50" t="n">
+        <v>-0.3619759289519581</v>
+      </c>
+      <c r="C50" t="n">
+        <v>-1.373074414992093</v>
+      </c>
+      <c r="D50" t="n">
+        <v>-2.660431542968581</v>
+      </c>
+      <c r="E50" t="n">
+        <v>0.4651104813797439</v>
+      </c>
+      <c r="F50" t="n">
+        <v>0.56939650131213</v>
+      </c>
+      <c r="G50" t="inlineStr"/>
+      <c r="H50" t="inlineStr"/>
+      <c r="I50" t="inlineStr"/>
+      <c r="J50" t="n">
+        <v>-0.199765576117666</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="1" t="inlineStr">
+        <is>
+          <t>C to L</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr"/>
+      <c r="C51" t="n">
+        <v>-0.426711202383301</v>
+      </c>
+      <c r="D51" t="inlineStr"/>
+      <c r="E51" t="inlineStr"/>
+      <c r="F51" t="inlineStr"/>
+      <c r="G51" t="inlineStr"/>
+      <c r="H51" t="inlineStr"/>
+      <c r="I51" t="inlineStr"/>
+      <c r="J51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="1" t="inlineStr">
+        <is>
+          <t>D to S</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr"/>
+      <c r="C52" t="n">
+        <v>-2.787275512924281</v>
+      </c>
+      <c r="D52" t="n">
+        <v>-3.575786687859065</v>
+      </c>
+      <c r="E52" t="inlineStr"/>
+      <c r="F52" t="inlineStr"/>
+      <c r="G52" t="inlineStr"/>
+      <c r="H52" t="inlineStr"/>
+      <c r="I52" t="inlineStr"/>
+      <c r="J52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="1" t="inlineStr">
+        <is>
+          <t>Q to S</t>
+        </is>
+      </c>
+      <c r="B53" t="n">
+        <v>-1.23279626936226</v>
+      </c>
+      <c r="C53" t="inlineStr"/>
+      <c r="D53" t="n">
+        <v>-1.445684801436449</v>
+      </c>
+      <c r="E53" t="inlineStr"/>
+      <c r="F53" t="n">
+        <v>-1.106924249194905</v>
+      </c>
+      <c r="G53" t="inlineStr"/>
+      <c r="H53" t="inlineStr"/>
+      <c r="I53" t="inlineStr"/>
+      <c r="J53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="1" t="inlineStr">
+        <is>
+          <t>G to D</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr"/>
+      <c r="C54" t="inlineStr"/>
+      <c r="D54" t="inlineStr"/>
+      <c r="E54" t="inlineStr"/>
+      <c r="F54" t="n">
+        <v>-3.332588846233692</v>
+      </c>
+      <c r="G54" t="inlineStr"/>
+      <c r="H54" t="inlineStr"/>
+      <c r="I54" t="inlineStr"/>
+      <c r="J54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="1" t="inlineStr">
+        <is>
+          <t>N to W</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr"/>
+      <c r="C55" t="n">
+        <v>-3.307134449087422</v>
+      </c>
+      <c r="D55" t="inlineStr"/>
+      <c r="E55" t="inlineStr"/>
+      <c r="F55" t="inlineStr"/>
+      <c r="G55" t="inlineStr"/>
+      <c r="H55" t="inlineStr"/>
+      <c r="I55" t="inlineStr"/>
+      <c r="J55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="1" t="inlineStr">
+        <is>
+          <t>L to M</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr"/>
+      <c r="C56" t="n">
+        <v>-2.48632531280486</v>
+      </c>
+      <c r="D56" t="n">
+        <v>0.8426790382942004</v>
+      </c>
+      <c r="E56" t="n">
+        <v>-0.626259430665565</v>
+      </c>
+      <c r="F56" t="inlineStr"/>
+      <c r="G56" t="inlineStr"/>
+      <c r="H56" t="inlineStr"/>
+      <c r="I56" t="inlineStr"/>
+      <c r="J56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="1" t="inlineStr">
+        <is>
+          <t>T to M</t>
+        </is>
+      </c>
+      <c r="B57" t="n">
+        <v>-1.85195967483441</v>
+      </c>
+      <c r="C57" t="n">
+        <v>-1.140325000105339</v>
+      </c>
+      <c r="D57" t="n">
+        <v>-2.287946030050484</v>
+      </c>
+      <c r="E57" t="inlineStr"/>
+      <c r="F57" t="inlineStr"/>
+      <c r="G57" t="inlineStr"/>
+      <c r="H57" t="inlineStr"/>
+      <c r="I57" t="n">
+        <v>-0.407719227618217</v>
+      </c>
+      <c r="J57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="1" t="inlineStr">
+        <is>
+          <t>E to N</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr"/>
+      <c r="C58" t="n">
+        <v>-2.237451275449977</v>
+      </c>
+      <c r="D58" t="n">
+        <v>-0.1590457199295772</v>
+      </c>
+      <c r="E58" t="n">
+        <v>-0.9524174244203687</v>
+      </c>
+      <c r="F58" t="n">
+        <v>-0.7044981490986285</v>
+      </c>
+      <c r="G58" t="inlineStr"/>
+      <c r="H58" t="inlineStr"/>
+      <c r="I58" t="inlineStr"/>
+      <c r="J58" t="n">
+        <v>-0.8121510520842383</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="1" t="inlineStr">
+        <is>
+          <t>C to S</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr"/>
+      <c r="C59" t="n">
+        <v>-2.316117954734697</v>
+      </c>
+      <c r="D59" t="inlineStr"/>
+      <c r="E59" t="n">
+        <v>0.2475281446492634</v>
+      </c>
+      <c r="F59" t="inlineStr"/>
+      <c r="G59" t="inlineStr"/>
+      <c r="H59" t="inlineStr"/>
+      <c r="I59" t="inlineStr"/>
+      <c r="J59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="1" t="inlineStr">
+        <is>
+          <t>F to V</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr"/>
+      <c r="C60" t="inlineStr"/>
+      <c r="D60" t="n">
+        <v>-1.805125674162293</v>
+      </c>
+      <c r="E60" t="inlineStr"/>
+      <c r="F60" t="inlineStr"/>
+      <c r="G60" t="inlineStr"/>
+      <c r="H60" t="inlineStr"/>
+      <c r="I60" t="inlineStr"/>
+      <c r="J60" t="n">
+        <v>-1.921609425869048</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="1" t="inlineStr">
+        <is>
+          <t>E to G</t>
+        </is>
+      </c>
+      <c r="B61" t="n">
+        <v>-2.88830992385652</v>
+      </c>
+      <c r="C61" t="inlineStr"/>
+      <c r="D61" t="inlineStr"/>
+      <c r="E61" t="inlineStr"/>
+      <c r="F61" t="inlineStr"/>
+      <c r="G61" t="inlineStr"/>
+      <c r="H61" t="inlineStr"/>
+      <c r="I61" t="inlineStr"/>
+      <c r="J61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="1" t="inlineStr">
+        <is>
+          <t>T to N</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr"/>
+      <c r="C62" t="n">
+        <v>-0.6238263367740313</v>
+      </c>
+      <c r="D62" t="inlineStr"/>
+      <c r="E62" t="inlineStr"/>
+      <c r="F62" t="inlineStr"/>
+      <c r="G62" t="inlineStr"/>
+      <c r="H62" t="inlineStr"/>
+      <c r="I62" t="inlineStr"/>
+      <c r="J62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="1" t="inlineStr">
+        <is>
+          <t>V to T</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr"/>
+      <c r="C63" t="inlineStr"/>
+      <c r="D63" t="inlineStr"/>
+      <c r="E63" t="inlineStr"/>
+      <c r="F63" t="inlineStr"/>
+      <c r="G63" t="n">
+        <v>-1.032904371040323</v>
+      </c>
+      <c r="H63" t="n">
+        <v>-1.08387495050386</v>
+      </c>
+      <c r="I63" t="n">
+        <v>-1.55980146622518</v>
+      </c>
+      <c r="J63" t="n">
+        <v>-0.6942173195136743</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="1" t="inlineStr">
+        <is>
+          <t>R to F</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr"/>
+      <c r="C64" t="inlineStr"/>
+      <c r="D64" t="n">
+        <v>-3.723608927536477</v>
+      </c>
+      <c r="E64" t="inlineStr"/>
+      <c r="F64" t="n">
+        <v>-2.538726963478933</v>
+      </c>
+      <c r="G64" t="n">
+        <v>-2.309567938984189</v>
+      </c>
+      <c r="H64" t="inlineStr"/>
+      <c r="I64" t="inlineStr"/>
+      <c r="J64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="1" t="inlineStr">
+        <is>
+          <t>L to F</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr"/>
+      <c r="C65" t="inlineStr"/>
+      <c r="D65" t="inlineStr"/>
+      <c r="E65" t="inlineStr"/>
+      <c r="F65" t="inlineStr"/>
+      <c r="G65" t="inlineStr"/>
+      <c r="H65" t="n">
+        <v>-0.899981324826351</v>
+      </c>
+      <c r="I65" t="inlineStr"/>
+      <c r="J65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="1" t="inlineStr">
+        <is>
+          <t>G to S</t>
+        </is>
+      </c>
+      <c r="B66" t="n">
+        <v>-0.5767748939216701</v>
+      </c>
+      <c r="C66" t="n">
+        <v>-1.867344538695529</v>
+      </c>
+      <c r="D66" t="n">
+        <v>-1.680621564513184</v>
+      </c>
+      <c r="E66" t="n">
+        <v>-1.240054774496784</v>
+      </c>
+      <c r="F66" t="n">
+        <v>-1.145403562826746</v>
+      </c>
+      <c r="G66" t="inlineStr"/>
+      <c r="H66" t="n">
+        <v>-0.2671777391037942</v>
+      </c>
+      <c r="I66" t="n">
+        <v>-2.014333161287967</v>
+      </c>
+      <c r="J66" t="n">
+        <v>-0.1457074917880983</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="1" t="inlineStr">
+        <is>
+          <t>S to Q</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr"/>
+      <c r="C67" t="inlineStr"/>
+      <c r="D67" t="n">
+        <v>-2.59329247009076</v>
+      </c>
+      <c r="E67" t="inlineStr"/>
+      <c r="F67" t="inlineStr"/>
+      <c r="G67" t="inlineStr"/>
+      <c r="H67" t="inlineStr"/>
+      <c r="I67" t="inlineStr"/>
+      <c r="J67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="1" t="inlineStr">
+        <is>
+          <t>V to D</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr"/>
+      <c r="C68" t="inlineStr"/>
+      <c r="D68" t="n">
+        <v>-2.183728068458488</v>
+      </c>
+      <c r="E68" t="inlineStr"/>
+      <c r="F68" t="inlineStr"/>
+      <c r="G68" t="inlineStr"/>
+      <c r="H68" t="n">
+        <v>-2.967080373055051</v>
+      </c>
+      <c r="I68" t="n">
+        <v>-2.880313915666053</v>
+      </c>
+      <c r="J68" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="1" t="inlineStr">
+        <is>
+          <t>G to T</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr"/>
+      <c r="C69" t="n">
+        <v>-2.894318537672504</v>
+      </c>
+      <c r="D69" t="n">
+        <v>-2.753593794502206</v>
+      </c>
+      <c r="E69" t="n">
+        <v>-2.69025097065938</v>
+      </c>
+      <c r="F69" t="n">
+        <v>-2.71539495085535</v>
+      </c>
+      <c r="G69" t="inlineStr"/>
+      <c r="H69" t="inlineStr"/>
+      <c r="I69" t="n">
+        <v>-3.111284070658823</v>
+      </c>
+      <c r="J69" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="1" t="inlineStr">
+        <is>
+          <t>C to Q</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr"/>
+      <c r="C70" t="inlineStr"/>
+      <c r="D70" t="inlineStr"/>
+      <c r="E70" t="inlineStr"/>
+      <c r="F70" t="inlineStr"/>
+      <c r="G70" t="inlineStr"/>
+      <c r="H70" t="inlineStr"/>
+      <c r="I70" t="n">
+        <v>0.7908317326202815</v>
+      </c>
+      <c r="J70" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="1" t="inlineStr">
+        <is>
+          <t>Y to D</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr"/>
+      <c r="C71" t="n">
+        <v>-2.560042482322975</v>
+      </c>
+      <c r="D71" t="n">
+        <v>-2.485620595764174</v>
+      </c>
+      <c r="E71" t="n">
+        <v>-3.551967336735547</v>
+      </c>
+      <c r="F71" t="n">
+        <v>-3.489202261351093</v>
+      </c>
+      <c r="G71" t="n">
+        <v>-3.491399292088542</v>
+      </c>
+      <c r="H71" t="n">
+        <v>-3.415935234463134</v>
+      </c>
+      <c r="I71" t="inlineStr"/>
+      <c r="J71" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="1" t="inlineStr">
+        <is>
+          <t>Q to G</t>
+        </is>
+      </c>
+      <c r="B72" t="n">
+        <v>-1.794045172584859</v>
+      </c>
+      <c r="C72" t="n">
+        <v>-2.154267559061348</v>
+      </c>
+      <c r="D72" t="n">
+        <v>-2.152155492403981</v>
+      </c>
+      <c r="E72" t="n">
+        <v>-2.03657745681114</v>
+      </c>
+      <c r="F72" t="n">
+        <v>-2.173609608975943</v>
+      </c>
+      <c r="G72" t="n">
+        <v>-1.824345062237293</v>
+      </c>
+      <c r="H72" t="inlineStr"/>
+      <c r="I72" t="n">
+        <v>-1.484838189593698</v>
+      </c>
+      <c r="J72" t="n">
+        <v>-1.860461281262108</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="1" t="inlineStr">
+        <is>
+          <t>G to A</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr"/>
+      <c r="C73" t="n">
+        <v>-0.1823659777842622</v>
+      </c>
+      <c r="D73" t="n">
+        <v>-2.411931735634147</v>
+      </c>
+      <c r="E73" t="inlineStr"/>
+      <c r="F73" t="inlineStr"/>
+      <c r="G73" t="inlineStr"/>
+      <c r="H73" t="n">
+        <v>-1.066484982489563</v>
+      </c>
+      <c r="I73" t="inlineStr"/>
+      <c r="J73" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" s="1" t="inlineStr">
+        <is>
+          <t>A to V</t>
+        </is>
+      </c>
+      <c r="B74" t="n">
+        <v>-0.842792084842353</v>
+      </c>
+      <c r="C74" t="n">
+        <v>-0.6827432293024183</v>
+      </c>
+      <c r="D74" t="n">
+        <v>-0.2358350772062613</v>
+      </c>
+      <c r="E74" t="n">
+        <v>-0.2492998169569994</v>
+      </c>
+      <c r="F74" t="n">
+        <v>-0.7874788780152924</v>
+      </c>
+      <c r="G74" t="n">
+        <v>-0.4314091091965606</v>
+      </c>
+      <c r="H74" t="n">
+        <v>-1.187371363352375</v>
+      </c>
+      <c r="I74" t="n">
+        <v>-0.2763637132023542</v>
+      </c>
+      <c r="J74" t="n">
+        <v>-0.6843746591178571</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="1" t="inlineStr">
+        <is>
+          <t>V to P</t>
+        </is>
+      </c>
+      <c r="B75" t="n">
+        <v>-2.584309820150518</v>
+      </c>
+      <c r="C75" t="n">
+        <v>-2.912086628695436</v>
+      </c>
+      <c r="D75" t="n">
+        <v>-2.429058369616511</v>
+      </c>
+      <c r="E75" t="n">
+        <v>-2.987823556727976</v>
+      </c>
+      <c r="F75" t="n">
+        <v>-2.761043752099446</v>
+      </c>
+      <c r="G75" t="n">
+        <v>-2.940665843753286</v>
+      </c>
+      <c r="H75" t="n">
+        <v>-1.904023614971769</v>
+      </c>
+      <c r="I75" t="n">
+        <v>-2.284933989736974</v>
+      </c>
+      <c r="J75" t="n">
+        <v>-1.896287695442513</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="1" t="inlineStr">
+        <is>
+          <t>H to N</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr"/>
+      <c r="C76" t="n">
+        <v>-3.4073369183034</v>
+      </c>
+      <c r="D76" t="n">
+        <v>-3.079977852096335</v>
+      </c>
+      <c r="E76" t="inlineStr"/>
+      <c r="F76" t="n">
+        <v>-3.082989942197915</v>
+      </c>
+      <c r="G76" t="n">
+        <v>-2.64729430026149</v>
+      </c>
+      <c r="H76" t="inlineStr"/>
+      <c r="I76" t="inlineStr"/>
+      <c r="J76" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" s="1" t="inlineStr">
+        <is>
+          <t>Q to N</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr"/>
+      <c r="C77" t="inlineStr"/>
+      <c r="D77" t="n">
+        <v>-3.734410497102615</v>
+      </c>
+      <c r="E77" t="inlineStr"/>
+      <c r="F77" t="inlineStr"/>
+      <c r="G77" t="inlineStr"/>
+      <c r="H77" t="inlineStr"/>
+      <c r="I77" t="inlineStr"/>
+      <c r="J77" t="n">
+        <v>0.03923659211084876</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="1" t="inlineStr">
+        <is>
+          <t>Q to T</t>
+        </is>
+      </c>
+      <c r="B78" t="n">
+        <v>-3.533636172483741</v>
+      </c>
+      <c r="C78" t="inlineStr"/>
+      <c r="D78" t="n">
+        <v>-3.859348177730011</v>
+      </c>
+      <c r="E78" t="inlineStr"/>
+      <c r="F78" t="n">
+        <v>-3.372093375654871</v>
+      </c>
+      <c r="G78" t="inlineStr"/>
+      <c r="H78" t="inlineStr"/>
+      <c r="I78" t="inlineStr"/>
+      <c r="J78" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" s="1" t="inlineStr">
+        <is>
+          <t>E to D</t>
+        </is>
+      </c>
+      <c r="B79" t="n">
+        <v>-0.5617770922280552</v>
+      </c>
+      <c r="C79" t="n">
+        <v>-0.2674458955549505</v>
+      </c>
+      <c r="D79" t="n">
+        <v>-0.461685726567532</v>
+      </c>
+      <c r="E79" t="n">
+        <v>-3.307443392197822</v>
+      </c>
+      <c r="F79" t="n">
+        <v>-1.34890728340116</v>
+      </c>
+      <c r="G79" t="n">
+        <v>-2.252365140703014</v>
+      </c>
+      <c r="H79" t="n">
+        <v>-0.1402739007300687</v>
+      </c>
+      <c r="I79" t="inlineStr"/>
+      <c r="J79" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" s="1" t="inlineStr">
+        <is>
+          <t>E to M</t>
+        </is>
+      </c>
+      <c r="B80" t="n">
+        <v>-1.4045412568839</v>
+      </c>
+      <c r="C80" t="n">
+        <v>-1.039955331970375</v>
+      </c>
+      <c r="D80" t="n">
+        <v>-3.047309517300068</v>
+      </c>
+      <c r="E80" t="n">
+        <v>-2.18610001545038</v>
+      </c>
+      <c r="F80" t="inlineStr"/>
+      <c r="G80" t="inlineStr"/>
+      <c r="H80" t="inlineStr"/>
+      <c r="I80" t="n">
+        <v>-1.826165737173533</v>
+      </c>
+      <c r="J80" t="n">
+        <v>-0.03919678934449775</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="1" t="inlineStr">
+        <is>
+          <t>Q to L</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr"/>
+      <c r="C81" t="inlineStr"/>
+      <c r="D81" t="inlineStr"/>
+      <c r="E81" t="n">
+        <v>-2.706631253492685</v>
+      </c>
+      <c r="F81" t="inlineStr"/>
+      <c r="G81" t="inlineStr"/>
+      <c r="H81" t="inlineStr"/>
+      <c r="I81" t="inlineStr"/>
+      <c r="J81" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" s="1" t="inlineStr">
+        <is>
+          <t>M to A</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr"/>
+      <c r="C82" t="inlineStr"/>
+      <c r="D82" t="inlineStr"/>
+      <c r="E82" t="inlineStr"/>
+      <c r="F82" t="inlineStr"/>
+      <c r="G82" t="inlineStr"/>
+      <c r="H82" t="inlineStr"/>
+      <c r="I82" t="n">
+        <v>-2.777573497801886</v>
+      </c>
+      <c r="J82" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" s="1" t="inlineStr">
+        <is>
+          <t>P to A</t>
+        </is>
+      </c>
+      <c r="B83" t="n">
+        <v>-1.856120487238615</v>
+      </c>
+      <c r="C83" t="n">
+        <v>-0.8806815241504841</v>
+      </c>
+      <c r="D83" t="n">
+        <v>-0.8159246892409555</v>
+      </c>
+      <c r="E83" t="n">
+        <v>-1.897554866263773</v>
+      </c>
+      <c r="F83" t="n">
+        <v>-0.5979145026090974</v>
+      </c>
+      <c r="G83" t="n">
+        <v>0.5606816666773493</v>
+      </c>
+      <c r="H83" t="inlineStr"/>
+      <c r="I83" t="n">
+        <v>-1.604269235462181</v>
+      </c>
+      <c r="J83" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" s="1" t="inlineStr">
+        <is>
+          <t>V to G</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr"/>
+      <c r="C84" t="inlineStr"/>
+      <c r="D84" t="n">
+        <v>-2.953212148393054</v>
+      </c>
+      <c r="E84" t="inlineStr"/>
+      <c r="F84" t="inlineStr"/>
+      <c r="G84" t="inlineStr"/>
+      <c r="H84" t="inlineStr"/>
+      <c r="I84" t="inlineStr"/>
+      <c r="J84" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" s="1" t="inlineStr">
+        <is>
+          <t>A to P</t>
+        </is>
+      </c>
+      <c r="B85" t="n">
+        <v>-2.709267638635628</v>
+      </c>
+      <c r="C85" t="n">
+        <v>-2.414682132065187</v>
+      </c>
+      <c r="D85" t="n">
+        <v>-2.630086340349047</v>
+      </c>
+      <c r="E85" t="n">
+        <v>-2.164443650368841</v>
+      </c>
+      <c r="F85" t="n">
+        <v>-2.055055819065081</v>
+      </c>
+      <c r="G85" t="inlineStr"/>
+      <c r="H85" t="n">
+        <v>-2.77165295737055</v>
+      </c>
+      <c r="I85" t="n">
+        <v>-2.742517488508346</v>
+      </c>
+      <c r="J85" t="n">
+        <v>-2.077821866150164</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="1" t="inlineStr">
+        <is>
+          <t>L to A</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr"/>
+      <c r="C86" t="inlineStr"/>
+      <c r="D86" t="n">
+        <v>-3.909290376416852</v>
+      </c>
+      <c r="E86" t="inlineStr"/>
+      <c r="F86" t="n">
+        <v>-3.844781729072009</v>
+      </c>
+      <c r="G86" t="inlineStr"/>
+      <c r="H86" t="inlineStr"/>
+      <c r="I86" t="n">
+        <v>-2.164189789044558</v>
+      </c>
+      <c r="J86" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" s="1" t="inlineStr">
+        <is>
+          <t>C to G</t>
+        </is>
+      </c>
+      <c r="B87" t="n">
+        <v>-1.604583302921172</v>
+      </c>
+      <c r="C87" t="inlineStr"/>
+      <c r="D87" t="n">
+        <v>-1.650305588338055</v>
+      </c>
+      <c r="E87" t="n">
+        <v>-1.498145046900468</v>
+      </c>
+      <c r="F87" t="n">
+        <v>-1.429114256626512</v>
+      </c>
+      <c r="G87" t="inlineStr"/>
+      <c r="H87" t="inlineStr"/>
+      <c r="I87" t="n">
+        <v>-1.349568003505391</v>
+      </c>
+      <c r="J87" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" s="1" t="inlineStr">
+        <is>
+          <t>Q to D</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr"/>
+      <c r="C88" t="inlineStr"/>
+      <c r="D88" t="inlineStr"/>
+      <c r="E88" t="n">
+        <v>-1.042611378017413</v>
+      </c>
+      <c r="F88" t="inlineStr"/>
+      <c r="G88" t="inlineStr"/>
+      <c r="H88" t="inlineStr"/>
+      <c r="I88" t="inlineStr"/>
+      <c r="J88" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" s="1" t="inlineStr">
+        <is>
+          <t>V to L</t>
+        </is>
+      </c>
+      <c r="B89" t="n">
+        <v>-0.2218024439116393</v>
+      </c>
+      <c r="C89" t="n">
+        <v>0.1438636017552057</v>
+      </c>
+      <c r="D89" t="n">
+        <v>0.1485259071760939</v>
+      </c>
+      <c r="E89" t="n">
+        <v>-0.3098260011460933</v>
+      </c>
+      <c r="F89" t="n">
+        <v>0.4917158689417664</v>
+      </c>
+      <c r="G89" t="n">
+        <v>0.9275109019293069</v>
+      </c>
+      <c r="H89" t="n">
+        <v>-0.6647695897368943</v>
+      </c>
+      <c r="I89" t="n">
+        <v>-0.4014014359762487</v>
+      </c>
+      <c r="J89" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" s="1" t="inlineStr">
+        <is>
+          <t>W to D</t>
+        </is>
+      </c>
+      <c r="B90" t="n">
+        <v>-2.729329311305865</v>
+      </c>
+      <c r="C90" t="n">
+        <v>-2.912235449231391</v>
+      </c>
+      <c r="D90" t="n">
+        <v>-2.893650219054222</v>
+      </c>
+      <c r="E90" t="n">
+        <v>-3.256695819609358</v>
+      </c>
+      <c r="F90" t="n">
+        <v>-3.030607253361953</v>
+      </c>
+      <c r="G90" t="n">
+        <v>-2.516152141190835</v>
+      </c>
+      <c r="H90" t="n">
+        <v>-2.329963604640621</v>
+      </c>
+      <c r="I90" t="inlineStr"/>
+      <c r="J90" t="n">
+        <v>-2.767722338315185</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="1" t="inlineStr">
+        <is>
+          <t>T to A</t>
+        </is>
+      </c>
+      <c r="B91" t="n">
+        <v>0.615813043047124</v>
+      </c>
+      <c r="C91" t="n">
+        <v>0.5989040691853931</v>
+      </c>
+      <c r="D91" t="n">
+        <v>-0.0746833914147976</v>
+      </c>
+      <c r="E91" t="n">
+        <v>-0.393329030527071</v>
+      </c>
+      <c r="F91" t="n">
+        <v>-0.4433521380929256</v>
+      </c>
+      <c r="G91" t="n">
+        <v>-0.02000105578085744</v>
+      </c>
+      <c r="H91" t="n">
+        <v>-0.6462654308030513</v>
+      </c>
+      <c r="I91" t="n">
+        <v>-0.03643995066707539</v>
+      </c>
+      <c r="J91" t="n">
+        <v>-0.7348949461174521</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="1" t="inlineStr">
+        <is>
+          <t>T to S</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr"/>
+      <c r="C92" t="n">
+        <v>-1.295801723881362</v>
+      </c>
+      <c r="D92" t="n">
+        <v>-2.326217374481129</v>
+      </c>
+      <c r="E92" t="n">
+        <v>-2.343313973296302</v>
+      </c>
+      <c r="F92" t="n">
+        <v>-1.772160073286773</v>
+      </c>
+      <c r="G92" t="n">
+        <v>-2.833818928435734</v>
+      </c>
+      <c r="H92" t="inlineStr"/>
+      <c r="I92" t="inlineStr"/>
+      <c r="J92" t="n">
+        <v>-2.441672052581193</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="1" t="inlineStr">
+        <is>
+          <t>C to A</t>
+        </is>
+      </c>
+      <c r="B93" t="n">
+        <v>1.307707474268436</v>
+      </c>
+      <c r="C93" t="inlineStr"/>
+      <c r="D93" t="inlineStr"/>
+      <c r="E93" t="inlineStr"/>
+      <c r="F93" t="inlineStr"/>
+      <c r="G93" t="inlineStr"/>
+      <c r="H93" t="inlineStr"/>
+      <c r="I93" t="inlineStr"/>
+      <c r="J93" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" s="1" t="inlineStr">
+        <is>
+          <t>L to W</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr"/>
+      <c r="C94" t="n">
+        <v>0.1766658738585115</v>
+      </c>
+      <c r="D94" t="n">
+        <v>-0.3662679896006025</v>
+      </c>
+      <c r="E94" t="inlineStr"/>
+      <c r="F94" t="inlineStr"/>
+      <c r="G94" t="inlineStr"/>
+      <c r="H94" t="inlineStr"/>
+      <c r="I94" t="inlineStr"/>
+      <c r="J94" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" s="1" t="inlineStr">
+        <is>
+          <t>A to N</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr"/>
+      <c r="C95" t="inlineStr"/>
+      <c r="D95" t="inlineStr"/>
+      <c r="E95" t="inlineStr"/>
+      <c r="F95" t="inlineStr"/>
+      <c r="G95" t="inlineStr"/>
+      <c r="H95" t="inlineStr"/>
+      <c r="I95" t="n">
+        <v>-2.410110894965205</v>
+      </c>
+      <c r="J95" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" s="1" t="inlineStr">
+        <is>
+          <t>H to Q</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr"/>
+      <c r="C96" t="inlineStr"/>
+      <c r="D96" t="inlineStr"/>
+      <c r="E96" t="n">
+        <v>-1.321711805379227</v>
+      </c>
+      <c r="F96" t="inlineStr"/>
+      <c r="G96" t="inlineStr"/>
+      <c r="H96" t="inlineStr"/>
+      <c r="I96" t="inlineStr"/>
+      <c r="J96" t="inlineStr"/>
+    </row>
+    <row r="97">
+      <c r="A97" s="1" t="inlineStr">
+        <is>
+          <t>G to C</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr"/>
+      <c r="C97" t="inlineStr"/>
+      <c r="D97" t="inlineStr"/>
+      <c r="E97" t="inlineStr"/>
+      <c r="F97" t="n">
+        <v>-1.356825021797972</v>
+      </c>
+      <c r="G97" t="inlineStr"/>
+      <c r="H97" t="inlineStr"/>
+      <c r="I97" t="inlineStr"/>
+      <c r="J97" t="inlineStr"/>
+    </row>
+    <row r="98">
+      <c r="A98" s="1" t="inlineStr">
+        <is>
+          <t>T to D</t>
+        </is>
+      </c>
+      <c r="B98" t="n">
+        <v>-2.771038271218387</v>
+      </c>
+      <c r="C98" t="n">
+        <v>-2.742913034251892</v>
+      </c>
+      <c r="D98" t="n">
+        <v>-2.979566184869936</v>
+      </c>
+      <c r="E98" t="n">
+        <v>-2.416728899830628</v>
+      </c>
+      <c r="F98" t="n">
+        <v>-2.442701282263832</v>
+      </c>
+      <c r="G98" t="n">
+        <v>-1.950273143660359</v>
+      </c>
+      <c r="H98" t="inlineStr"/>
+      <c r="I98" t="n">
+        <v>-2.496636445485056</v>
+      </c>
+      <c r="J98" t="n">
+        <v>-1.072414206849355</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="1" t="inlineStr">
+        <is>
+          <t>G to E</t>
+        </is>
+      </c>
+      <c r="B99" t="n">
+        <v>-1.994971094463009</v>
+      </c>
+      <c r="C99" t="inlineStr"/>
+      <c r="D99" t="n">
+        <v>-1.943874142887593</v>
+      </c>
+      <c r="E99" t="n">
+        <v>-1.409815740804866</v>
+      </c>
+      <c r="F99" t="n">
+        <v>-1.64652636017601</v>
+      </c>
+      <c r="G99" t="inlineStr"/>
+      <c r="H99" t="n">
+        <v>-1.079926535030604</v>
+      </c>
+      <c r="I99" t="n">
+        <v>-1.502360480503668</v>
+      </c>
+      <c r="J99" t="inlineStr"/>
+    </row>
+    <row r="100">
+      <c r="A100" s="1" t="inlineStr">
+        <is>
+          <t>A to D</t>
+        </is>
+      </c>
+      <c r="B100" t="n">
+        <v>-0.5332665582857818</v>
+      </c>
+      <c r="C100" t="inlineStr"/>
+      <c r="D100" t="inlineStr"/>
+      <c r="E100" t="inlineStr"/>
+      <c r="F100" t="inlineStr"/>
+      <c r="G100" t="n">
+        <v>-0.5675568401214499</v>
+      </c>
+      <c r="H100" t="n">
+        <v>-1.235863259318905</v>
+      </c>
+      <c r="I100" t="n">
+        <v>-1.529008166171974</v>
+      </c>
+      <c r="J100" t="n">
+        <v>0.2961007189974759</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="1" t="inlineStr">
+        <is>
+          <t>A to W</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr"/>
+      <c r="C101" t="inlineStr"/>
+      <c r="D101" t="n">
+        <v>-0.6298160070244047</v>
+      </c>
+      <c r="E101" t="inlineStr"/>
+      <c r="F101" t="inlineStr"/>
+      <c r="G101" t="inlineStr"/>
+      <c r="H101" t="inlineStr"/>
+      <c r="I101" t="inlineStr"/>
+      <c r="J101" t="inlineStr"/>
+    </row>
+    <row r="102">
+      <c r="A102" s="1" t="inlineStr">
+        <is>
+          <t>T to Q</t>
+        </is>
+      </c>
+      <c r="B102" t="n">
+        <v>-3.238175600283333</v>
+      </c>
+      <c r="C102" t="n">
+        <v>-2.467214884703536</v>
+      </c>
+      <c r="D102" t="n">
+        <v>-2.747143933794614</v>
+      </c>
+      <c r="E102" t="inlineStr"/>
+      <c r="F102" t="n">
+        <v>-2.888172762261488</v>
+      </c>
+      <c r="G102" t="inlineStr"/>
+      <c r="H102" t="n">
+        <v>-2.482770847537978</v>
+      </c>
+      <c r="I102" t="n">
+        <v>-2.322832158553919</v>
+      </c>
+      <c r="J102" t="inlineStr"/>
+    </row>
+    <row r="103">
+      <c r="A103" s="1" t="inlineStr">
+        <is>
+          <t>A to L</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr"/>
+      <c r="C103" t="inlineStr"/>
+      <c r="D103" t="inlineStr"/>
+      <c r="E103" t="inlineStr"/>
+      <c r="F103" t="inlineStr"/>
+      <c r="G103" t="inlineStr"/>
+      <c r="H103" t="inlineStr"/>
+      <c r="I103" t="n">
+        <v>0.6343489885830671</v>
+      </c>
+      <c r="J103" t="inlineStr"/>
+    </row>
+    <row r="104">
+      <c r="A104" s="1" t="inlineStr">
+        <is>
+          <t>P to N</t>
+        </is>
+      </c>
+      <c r="B104" t="n">
+        <v>-0.7962804120713747</v>
+      </c>
+      <c r="C104" t="n">
+        <v>-1.083215898640281</v>
+      </c>
+      <c r="D104" t="n">
+        <v>-1.007171568830983</v>
+      </c>
+      <c r="E104" t="n">
+        <v>-1.238895118302969</v>
+      </c>
+      <c r="F104" t="n">
+        <v>-1.720547953505342</v>
+      </c>
+      <c r="G104" t="n">
+        <v>-1.567003363756431</v>
+      </c>
+      <c r="H104" t="n">
+        <v>0.08321263116905223</v>
+      </c>
+      <c r="I104" t="n">
+        <v>-0.447434863148352</v>
+      </c>
+      <c r="J104" t="n">
+        <v>0.4471698695832014</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Dependencies/Analysis_Outputs/Ping_2018/Reporter_RAAS_byAAS_alldatasets.xlsx
+++ b/Dependencies/Analysis_Outputs/Ping_2018/Reporter_RAAS_byAAS_alldatasets.xlsx
@@ -483,87 +483,93 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>T to G</t>
+          <t>T to A</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>-1.824492557661394</v>
+        <v>0.6158106322651906</v>
       </c>
       <c r="C2" t="n">
-        <v>-3.01544633523496</v>
+        <v>0.5631040646903495</v>
       </c>
       <c r="D2" t="n">
-        <v>-3.025966020837576</v>
+        <v>-0.05873273195186385</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.8123735133237393</v>
+        <v>-0.3882789170631177</v>
       </c>
       <c r="F2" t="n">
-        <v>-1.016908187940959</v>
-      </c>
-      <c r="G2" t="n">
-        <v>-2.037173842938715</v>
-      </c>
+        <v>-0.4779700911410305</v>
+      </c>
+      <c r="G2" t="inlineStr"/>
       <c r="H2" t="n">
-        <v>-2.021652997820707</v>
-      </c>
-      <c r="I2" t="inlineStr"/>
+        <v>0.0501144684486006</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0.8457255883973716</v>
+      </c>
       <c r="J2" t="n">
-        <v>-1.60635625247893</v>
+        <v>-0.0316255295385095</v>
       </c>
       <c r="K2" t="n">
-        <v>-2.536178496201575</v>
+        <v>-1.189264442513201</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>S to C</t>
+          <t>C to G</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-1.119477822045281</v>
+        <v>-1.604583302921172</v>
       </c>
       <c r="C3" t="n">
-        <v>-0.5420251763689677</v>
+        <v>-1.653379736453924</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.76889570955057</v>
+        <v>-1.650305588338055</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.9980608897109512</v>
+        <v>-1.498145046900468</v>
       </c>
       <c r="F3" t="n">
-        <v>0.1052649444633963</v>
-      </c>
-      <c r="G3" t="n">
-        <v>-1.420409791970981</v>
-      </c>
+        <v>-1.429114256626512</v>
+      </c>
+      <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="n">
-        <v>-1.696480754036708</v>
-      </c>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>V to G</t>
+          <t>M to T</t>
         </is>
       </c>
       <c r="B4" t="inlineStr"/>
-      <c r="C4" t="inlineStr"/>
-      <c r="D4" t="n">
-        <v>-2.953212148393054</v>
-      </c>
+      <c r="C4" t="n">
+        <v>-2.997671962076633</v>
+      </c>
+      <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
+      <c r="G4" t="n">
+        <v>-2.897380778067156</v>
+      </c>
+      <c r="H4" t="n">
+        <v>-2.49346593273689</v>
+      </c>
+      <c r="I4" t="n">
+        <v>-2.143942079674241</v>
+      </c>
+      <c r="J4" t="n">
+        <v>-2.129683849273043</v>
+      </c>
+      <c r="K4" t="n">
+        <v>-2.802777599482629</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
@@ -587,75 +593,67 @@
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>G to A</t>
+          <t>P to Q</t>
         </is>
       </c>
       <c r="B6" t="inlineStr"/>
-      <c r="C6" t="n">
-        <v>-0.1823659777842622</v>
-      </c>
-      <c r="D6" t="n">
-        <v>-2.730527398715791</v>
-      </c>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
+      <c r="F6" t="n">
+        <v>-3.126724744137131</v>
+      </c>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr"/>
-      <c r="I6" t="n">
-        <v>-0.1214902790354423</v>
-      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>Q to G</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>-1.631396635803113</v>
-      </c>
-      <c r="C7" t="n">
-        <v>-2.019896936152168</v>
-      </c>
-      <c r="D7" t="n">
-        <v>-2.428508034998956</v>
-      </c>
-      <c r="E7" t="n">
-        <v>-2.230292925826905</v>
-      </c>
-      <c r="F7" t="n">
-        <v>-2.174714118913573</v>
-      </c>
-      <c r="G7" t="n">
-        <v>-1.427040646908441</v>
-      </c>
-      <c r="H7" t="n">
-        <v>-1.882813650363043</v>
-      </c>
+          <t>T to I/L</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr"/>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="n">
-        <v>-1.606837129471362</v>
-      </c>
-      <c r="K7" t="n">
-        <v>-1.514233604564605</v>
-      </c>
+        <v>1.945140599196265</v>
+      </c>
+      <c r="K7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>T to C</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr"/>
-      <c r="C8" t="inlineStr"/>
-      <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
+          <t>P to A</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>-1.865159710553465</v>
+      </c>
+      <c r="C8" t="n">
+        <v>-0.8853371665991663</v>
+      </c>
+      <c r="D8" t="n">
+        <v>-1.354458591812705</v>
+      </c>
+      <c r="E8" t="n">
+        <v>-1.797264822207178</v>
+      </c>
+      <c r="F8" t="n">
+        <v>-0.08751827316426125</v>
+      </c>
+      <c r="G8" t="n">
+        <v>-0.04723405743084132</v>
+      </c>
       <c r="H8" t="n">
-        <v>-2.772021341363324</v>
+        <v>0.4707840653703282</v>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
@@ -664,105 +662,133 @@
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>V to D</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr"/>
-      <c r="C9" t="inlineStr"/>
+          <t>S to N</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>-1.923244617955385</v>
+      </c>
+      <c r="C9" t="n">
+        <v>-1.486417520558868</v>
+      </c>
       <c r="D9" t="n">
-        <v>-2.369744228178009</v>
-      </c>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
+        <v>-0.02770557365823363</v>
+      </c>
+      <c r="E9" t="n">
+        <v>-2.831575369234201</v>
+      </c>
+      <c r="F9" t="n">
+        <v>-1.065549125598596</v>
+      </c>
       <c r="G9" t="n">
-        <v>-2.741604498435132</v>
+        <v>-1.63978401181236</v>
       </c>
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
+      <c r="J9" t="n">
+        <v>-2.036148144902004</v>
+      </c>
       <c r="K9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>M to F</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr"/>
-      <c r="C10" t="inlineStr"/>
-      <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr"/>
+          <t>V to I/L</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>-0.01766140843393098</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0.03107672106072522</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0.1900077366633942</v>
+      </c>
+      <c r="E10" t="n">
+        <v>-1.338706592904841</v>
+      </c>
       <c r="F10" t="n">
-        <v>-2.089286415298105</v>
-      </c>
-      <c r="G10" t="inlineStr"/>
+        <v>0.3464496316642493</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.2434189947951148</v>
+      </c>
       <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
+      <c r="I10" t="n">
+        <v>-0.3253046634918442</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0.03609218343390806</v>
+      </c>
       <c r="K10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>L to S</t>
+          <t>A to I/L</t>
         </is>
       </c>
       <c r="B11" t="inlineStr"/>
-      <c r="C11" t="n">
-        <v>-3.303445692792092</v>
-      </c>
-      <c r="D11" t="n">
-        <v>-3.543628069658578</v>
-      </c>
-      <c r="E11" t="n">
-        <v>-3.67230027388256</v>
-      </c>
-      <c r="F11" t="n">
-        <v>-3.575121950461244</v>
-      </c>
-      <c r="G11" t="n">
-        <v>-3.422816315225209</v>
-      </c>
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="n">
-        <v>-3.318062107134399</v>
+        <v>0.6343467865506169</v>
       </c>
       <c r="K11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>F to V</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr"/>
-      <c r="C12" t="inlineStr"/>
-      <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr"/>
+          <t>T to D</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>-2.708323957439661</v>
+      </c>
+      <c r="C12" t="n">
+        <v>-2.313812233553072</v>
+      </c>
+      <c r="D12" t="n">
+        <v>-2.991903582271612</v>
+      </c>
+      <c r="E12" t="n">
+        <v>-2.323665623467106</v>
+      </c>
+      <c r="F12" t="n">
+        <v>-2.693899350223147</v>
+      </c>
       <c r="G12" t="n">
-        <v>-1.810759626831118</v>
-      </c>
-      <c r="H12" t="inlineStr"/>
+        <v>-2.006419287849925</v>
+      </c>
+      <c r="H12" t="n">
+        <v>-2.302819058631381</v>
+      </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
+      <c r="J12" t="n">
+        <v>-2.297724439443744</v>
+      </c>
+      <c r="K12" t="n">
+        <v>-1.141653233714327</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>T to N</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr"/>
-      <c r="C13" t="n">
-        <v>-0.8856825678462671</v>
-      </c>
+          <t>E to G</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>-2.88830992385652</v>
+      </c>
+      <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr"/>
-      <c r="E13" t="n">
-        <v>-0.9073352310048021</v>
-      </c>
+      <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr"/>
@@ -773,85 +799,83 @@
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>S to N</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
-        <v>-1.923244617955385</v>
-      </c>
-      <c r="C14" t="n">
-        <v>-1.486417520558868</v>
-      </c>
-      <c r="D14" t="n">
-        <v>-0.02770557365823363</v>
-      </c>
+          <t>Y to D</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr"/>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="inlineStr"/>
       <c r="E14" t="n">
-        <v>-2.831575369234201</v>
+        <v>-5.00917166544131</v>
       </c>
       <c r="F14" t="n">
-        <v>-1.065549125598596</v>
-      </c>
-      <c r="G14" t="n">
-        <v>-1.63978401181236</v>
-      </c>
-      <c r="H14" t="inlineStr"/>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="n">
-        <v>-2.036148144902004</v>
-      </c>
+        <v>-3.463652883592532</v>
+      </c>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="n">
+        <v>-3.001880951613521</v>
+      </c>
+      <c r="I14" t="n">
+        <v>-3.44591734749921</v>
+      </c>
+      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>N to M</t>
+          <t>P to T</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>-1.896177495696552</v>
+        <v>-1.378795339808385</v>
       </c>
       <c r="C15" t="n">
-        <v>-1.862261963638834</v>
+        <v>-1.388568315633956</v>
       </c>
       <c r="D15" t="n">
-        <v>-1.903982009937961</v>
+        <v>-1.856271864209096</v>
       </c>
       <c r="E15" t="n">
-        <v>-2.184650077067929</v>
+        <v>-1.644315982108478</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.854069456964569</v>
-      </c>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr"/>
-      <c r="I15" t="inlineStr"/>
+        <v>-1.774377006173016</v>
+      </c>
+      <c r="G15" t="n">
+        <v>-0.4833337585628716</v>
+      </c>
+      <c r="H15" t="n">
+        <v>-1.26882658524452</v>
+      </c>
+      <c r="I15" t="n">
+        <v>-1.333824698279085</v>
+      </c>
       <c r="J15" t="n">
-        <v>-1.864916815978686</v>
+        <v>-1.669105188879012</v>
       </c>
       <c r="K15" t="n">
-        <v>-1.95474476750725</v>
+        <v>-0.652745001026258</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>M to G</t>
+          <t>P to S</t>
         </is>
       </c>
       <c r="B16" t="inlineStr"/>
       <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr"/>
-      <c r="E16" t="n">
-        <v>-1.506132862323145</v>
-      </c>
-      <c r="F16" t="n">
-        <v>-2.073913401043293</v>
-      </c>
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
+      <c r="K16" t="n">
+        <v>-0.8861326021807104</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
@@ -883,90 +907,100 @@
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>T to M</t>
+          <t>Q to D</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>-1.797361614849641</v>
-      </c>
-      <c r="C18" t="n">
-        <v>-1.140338657533766</v>
-      </c>
-      <c r="D18" t="n">
-        <v>-1.634221640465138</v>
-      </c>
-      <c r="E18" t="inlineStr"/>
+        <v>-1.042250049799073</v>
+      </c>
+      <c r="C18" t="inlineStr"/>
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="n">
+        <v>-0.6897540732350171</v>
+      </c>
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="n">
-        <v>-0.4870746016522467</v>
-      </c>
+      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>P to Q</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr"/>
-      <c r="C19" t="inlineStr"/>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr"/>
+          <t>V to P</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>-2.583764170393808</v>
+      </c>
+      <c r="C19" t="n">
+        <v>-2.836952077708304</v>
+      </c>
+      <c r="D19" t="n">
+        <v>-2.840879999337838</v>
+      </c>
+      <c r="E19" t="n">
+        <v>-1.590057630217481</v>
+      </c>
       <c r="F19" t="n">
-        <v>-3.126724744137131</v>
-      </c>
-      <c r="G19" t="inlineStr"/>
+        <v>-2.612182277852697</v>
+      </c>
+      <c r="G19" t="n">
+        <v>-1.324515837623609</v>
+      </c>
       <c r="H19" t="inlineStr"/>
-      <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
+      <c r="I19" t="n">
+        <v>-1.996818007175048</v>
+      </c>
+      <c r="J19" t="n">
+        <v>-2.498637884414341</v>
+      </c>
       <c r="K19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>A to S</t>
+          <t>T to M</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>-0.9111511500362017</v>
+        <v>-1.797361614849641</v>
       </c>
       <c r="C20" t="n">
-        <v>-2.334597233133084</v>
+        <v>-1.140338657533766</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.00095240365475</v>
-      </c>
-      <c r="E20" t="n">
-        <v>-2.21581847002445</v>
-      </c>
-      <c r="F20" t="n">
-        <v>-2.962753222493237</v>
-      </c>
-      <c r="G20" t="n">
-        <v>-0.690198438333234</v>
-      </c>
+        <v>-1.634221640465138</v>
+      </c>
+      <c r="E20" t="inlineStr"/>
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="inlineStr"/>
       <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="n">
-        <v>-2.117965233820735</v>
-      </c>
+      <c r="J20" t="n">
+        <v>-0.4870746016522467</v>
+      </c>
+      <c r="K20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>Q to V</t>
+          <t>D to M</t>
         </is>
       </c>
       <c r="B21" t="inlineStr"/>
-      <c r="C21" t="inlineStr"/>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr"/>
+      <c r="C21" t="n">
+        <v>-1.708101373184544</v>
+      </c>
+      <c r="D21" t="n">
+        <v>0.6947551869677342</v>
+      </c>
+      <c r="E21" t="n">
+        <v>-1.257065657302828</v>
+      </c>
       <c r="F21" t="n">
-        <v>2.000873105475007</v>
+        <v>-1.053772409055846</v>
       </c>
       <c r="G21" t="inlineStr"/>
       <c r="H21" t="inlineStr"/>
@@ -977,256 +1011,218 @@
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>G to Q</t>
+          <t>L to E</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>-2.332913290549719</v>
-      </c>
-      <c r="C22" t="n">
-        <v>-2.851837270175408</v>
-      </c>
-      <c r="D22" t="n">
-        <v>-2.8355823200199</v>
-      </c>
-      <c r="E22" t="n">
-        <v>-2.434241835029978</v>
-      </c>
-      <c r="F22" t="n">
-        <v>-2.499741892092826</v>
-      </c>
-      <c r="G22" t="n">
-        <v>-2.31814227672377</v>
-      </c>
-      <c r="H22" t="n">
-        <v>-2.073985146743326</v>
-      </c>
+        <v>-0.3139181578271339</v>
+      </c>
+      <c r="C22" t="inlineStr"/>
+      <c r="D22" t="inlineStr"/>
+      <c r="E22" t="inlineStr"/>
+      <c r="F22" t="inlineStr"/>
+      <c r="G22" t="inlineStr"/>
+      <c r="H22" t="inlineStr"/>
       <c r="I22" t="inlineStr"/>
-      <c r="J22" t="n">
-        <v>-2.949282404433042</v>
-      </c>
+      <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>V to P</t>
-        </is>
-      </c>
-      <c r="B23" t="n">
-        <v>-2.583764170393808</v>
-      </c>
-      <c r="C23" t="n">
-        <v>-2.836952077708304</v>
-      </c>
-      <c r="D23" t="n">
-        <v>-2.840879999337838</v>
-      </c>
-      <c r="E23" t="n">
-        <v>-1.590057630217481</v>
-      </c>
-      <c r="F23" t="n">
-        <v>-2.612182277852697</v>
-      </c>
+          <t>V to Q</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr"/>
+      <c r="C23" t="inlineStr"/>
+      <c r="D23" t="inlineStr"/>
+      <c r="E23" t="inlineStr"/>
+      <c r="F23" t="inlineStr"/>
       <c r="G23" t="n">
-        <v>-1.324515837623609</v>
+        <v>-1.557785451729937</v>
       </c>
       <c r="H23" t="inlineStr"/>
-      <c r="I23" t="n">
-        <v>-1.996818007175048</v>
-      </c>
-      <c r="J23" t="n">
-        <v>-2.498637884414341</v>
-      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>G to S</t>
+          <t>I to V</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>-1.745077699105976</v>
+        <v>0.2964127259572112</v>
       </c>
       <c r="C24" t="n">
-        <v>-1.866754888350168</v>
+        <v>-0.3204300206009085</v>
       </c>
       <c r="D24" t="n">
-        <v>-2.080123011830736</v>
+        <v>-0.2853090975187899</v>
       </c>
       <c r="E24" t="n">
-        <v>0.02179676844025173</v>
+        <v>0.1675091654826392</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.142756069897438</v>
+        <v>-0.3529848185555949</v>
       </c>
       <c r="G24" t="n">
-        <v>-0.1318026355199155</v>
-      </c>
-      <c r="H24" t="inlineStr"/>
+        <v>-0.2201549293866399</v>
+      </c>
+      <c r="H24" t="n">
+        <v>-1.794348501532178</v>
+      </c>
       <c r="I24" t="inlineStr"/>
       <c r="J24" t="n">
-        <v>-2.014333161287967</v>
-      </c>
-      <c r="K24" t="inlineStr"/>
+        <v>-1.025394863591695</v>
+      </c>
+      <c r="K24" t="n">
+        <v>-1.234195473178331</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>A to D</t>
+          <t>H to N</t>
         </is>
       </c>
       <c r="B25" t="inlineStr"/>
       <c r="C25" t="inlineStr"/>
       <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr"/>
-      <c r="F25" t="inlineStr"/>
+      <c r="E25" t="n">
+        <v>-3.278180091207601</v>
+      </c>
+      <c r="F25" t="n">
+        <v>-3.039534065436603</v>
+      </c>
       <c r="G25" t="inlineStr"/>
-      <c r="H25" t="n">
-        <v>-0.5675460116554798</v>
-      </c>
-      <c r="I25" t="n">
-        <v>-1.235863259318905</v>
-      </c>
-      <c r="J25" t="n">
-        <v>-1.48745941186576</v>
-      </c>
-      <c r="K25" t="n">
-        <v>0.2961007189974759</v>
-      </c>
+      <c r="H25" t="inlineStr"/>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>A to I/L</t>
+          <t>A to Q</t>
         </is>
       </c>
       <c r="B26" t="inlineStr"/>
       <c r="C26" t="inlineStr"/>
       <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr"/>
+      <c r="E26" t="n">
+        <v>-2.274948617468515</v>
+      </c>
       <c r="F26" t="inlineStr"/>
-      <c r="G26" t="inlineStr"/>
+      <c r="G26" t="n">
+        <v>-2.328055224162954</v>
+      </c>
       <c r="H26" t="inlineStr"/>
-      <c r="I26" t="inlineStr"/>
-      <c r="J26" t="n">
-        <v>0.6343467865506169</v>
-      </c>
+      <c r="I26" t="n">
+        <v>-1.952558442403316</v>
+      </c>
+      <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>L to A</t>
+          <t>N to I/L</t>
         </is>
       </c>
       <c r="B27" t="inlineStr"/>
       <c r="C27" t="inlineStr"/>
       <c r="D27" t="inlineStr"/>
-      <c r="E27" t="n">
-        <v>-2.468588850198645</v>
-      </c>
+      <c r="E27" t="inlineStr"/>
       <c r="F27" t="inlineStr"/>
-      <c r="G27" t="inlineStr"/>
+      <c r="G27" t="n">
+        <v>-0.7119494631216526</v>
+      </c>
       <c r="H27" t="inlineStr"/>
       <c r="I27" t="inlineStr"/>
-      <c r="J27" t="n">
-        <v>-2.164312730203802</v>
-      </c>
+      <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>N to S</t>
-        </is>
-      </c>
-      <c r="B28" t="n">
-        <v>-1.220899976660314</v>
-      </c>
-      <c r="C28" t="n">
-        <v>-2.051238538092127</v>
-      </c>
-      <c r="D28" t="n">
-        <v>-1.767355338190012</v>
-      </c>
+          <t>L to A</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr"/>
+      <c r="C28" t="inlineStr"/>
+      <c r="D28" t="inlineStr"/>
       <c r="E28" t="n">
-        <v>-0.8687846315630907</v>
+        <v>-2.468588850198645</v>
       </c>
       <c r="F28" t="inlineStr"/>
-      <c r="G28" t="n">
-        <v>-1.351173262866905</v>
-      </c>
+      <c r="G28" t="inlineStr"/>
       <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr"/>
       <c r="J28" t="n">
-        <v>-1.591116997728084</v>
-      </c>
-      <c r="K28" t="n">
-        <v>-1.253467642702373</v>
-      </c>
+        <v>-2.164312730203802</v>
+      </c>
+      <c r="K28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>P to S</t>
+          <t>M to F</t>
         </is>
       </c>
       <c r="B29" t="inlineStr"/>
       <c r="C29" t="inlineStr"/>
       <c r="D29" t="inlineStr"/>
       <c r="E29" t="inlineStr"/>
-      <c r="F29" t="inlineStr"/>
+      <c r="F29" t="n">
+        <v>-2.089286415298105</v>
+      </c>
       <c r="G29" t="inlineStr"/>
       <c r="H29" t="inlineStr"/>
       <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr"/>
-      <c r="K29" t="n">
-        <v>-0.8861326021807104</v>
-      </c>
+      <c r="K29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>I to T</t>
-        </is>
-      </c>
-      <c r="B30" t="n">
-        <v>2.315423482620839</v>
-      </c>
+          <t>C to S</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr"/>
       <c r="C30" t="n">
-        <v>-3.117670437503977</v>
+        <v>-1.844028167018038</v>
       </c>
       <c r="D30" t="inlineStr"/>
-      <c r="E30" t="inlineStr"/>
+      <c r="E30" t="n">
+        <v>0.2475281446492634</v>
+      </c>
       <c r="F30" t="inlineStr"/>
-      <c r="G30" t="inlineStr"/>
+      <c r="G30" t="n">
+        <v>-0.9407052210779292</v>
+      </c>
       <c r="H30" t="inlineStr"/>
       <c r="I30" t="inlineStr"/>
-      <c r="J30" t="n">
-        <v>-2.418029242897276</v>
-      </c>
+      <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>E to N</t>
+          <t>L to M</t>
         </is>
       </c>
       <c r="B31" t="inlineStr"/>
-      <c r="C31" t="inlineStr"/>
+      <c r="C31" t="n">
+        <v>-0.8374896289325378</v>
+      </c>
       <c r="D31" t="inlineStr"/>
       <c r="E31" t="n">
-        <v>-1.050732675513399</v>
-      </c>
-      <c r="F31" t="n">
-        <v>-1.747000236646142</v>
-      </c>
-      <c r="G31" t="n">
-        <v>-1.611690933862995</v>
-      </c>
+        <v>-1.778352863980573</v>
+      </c>
+      <c r="F31" t="inlineStr"/>
+      <c r="G31" t="inlineStr"/>
       <c r="H31" t="inlineStr"/>
       <c r="I31" t="inlineStr"/>
       <c r="J31" t="inlineStr"/>
@@ -1235,18 +1231,28 @@
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>N to I/L</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr"/>
-      <c r="C32" t="inlineStr"/>
-      <c r="D32" t="inlineStr"/>
-      <c r="E32" t="inlineStr"/>
-      <c r="F32" t="inlineStr"/>
-      <c r="G32" t="n">
-        <v>-0.7119494631216526</v>
-      </c>
-      <c r="H32" t="inlineStr"/>
+          <t>S to G</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>-2.867905793283137</v>
+      </c>
+      <c r="C32" t="n">
+        <v>-1.524159150723433</v>
+      </c>
+      <c r="D32" t="n">
+        <v>0.9660662627030125</v>
+      </c>
+      <c r="E32" t="n">
+        <v>-1.706136224905055</v>
+      </c>
+      <c r="F32" t="n">
+        <v>-2.151722908579604</v>
+      </c>
+      <c r="G32" t="inlineStr"/>
+      <c r="H32" t="n">
+        <v>-0.946960170181026</v>
+      </c>
       <c r="I32" t="inlineStr"/>
       <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr"/>
@@ -1254,132 +1260,178 @@
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>H to D</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr"/>
-      <c r="C33" t="inlineStr"/>
-      <c r="D33" t="inlineStr"/>
-      <c r="E33" t="inlineStr"/>
+          <t>V to A</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>-0.8072930572314686</v>
+      </c>
+      <c r="C33" t="n">
+        <v>0.01355251416744737</v>
+      </c>
+      <c r="D33" t="n">
+        <v>2.071131702541749</v>
+      </c>
+      <c r="E33" t="n">
+        <v>-1.858940607856459</v>
+      </c>
       <c r="F33" t="n">
-        <v>-1.861486441134107</v>
-      </c>
-      <c r="G33" t="inlineStr"/>
-      <c r="H33" t="inlineStr"/>
-      <c r="I33" t="inlineStr"/>
+        <v>-0.2921806432411803</v>
+      </c>
+      <c r="G33" t="n">
+        <v>0.5994838204215935</v>
+      </c>
+      <c r="H33" t="n">
+        <v>0.07325158936121866</v>
+      </c>
+      <c r="I33" t="n">
+        <v>0.5272452090096513</v>
+      </c>
       <c r="J33" t="n">
-        <v>-1.932831549924681</v>
-      </c>
-      <c r="K33" t="inlineStr"/>
+        <v>-1.278681972903824</v>
+      </c>
+      <c r="K33" t="n">
+        <v>1.341952077388964</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>A to T</t>
-        </is>
-      </c>
-      <c r="B34" t="n">
-        <v>0.02875263253085487</v>
-      </c>
+          <t>C to I/L</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr"/>
       <c r="C34" t="n">
-        <v>-0.4228200836303959</v>
-      </c>
-      <c r="D34" t="n">
-        <v>-1.409847034239312</v>
-      </c>
-      <c r="E34" t="n">
-        <v>-0.04673617028414147</v>
-      </c>
-      <c r="F34" t="n">
-        <v>-0.1182077753621543</v>
-      </c>
+        <v>-0.2614433172230166</v>
+      </c>
+      <c r="D34" t="inlineStr"/>
+      <c r="E34" t="inlineStr"/>
+      <c r="F34" t="inlineStr"/>
       <c r="G34" t="inlineStr"/>
       <c r="H34" t="inlineStr"/>
       <c r="I34" t="inlineStr"/>
-      <c r="J34" t="n">
-        <v>-1.376424251288294</v>
-      </c>
-      <c r="K34" t="n">
-        <v>-1.496902947068001</v>
-      </c>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>Y to D</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr"/>
-      <c r="C35" t="inlineStr"/>
-      <c r="D35" t="inlineStr"/>
+          <t>A to S</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>-0.9111511500362017</v>
+      </c>
+      <c r="C35" t="n">
+        <v>-2.334597233133084</v>
+      </c>
+      <c r="D35" t="n">
+        <v>-2.00095240365475</v>
+      </c>
       <c r="E35" t="n">
-        <v>-5.00917166544131</v>
+        <v>-2.21581847002445</v>
       </c>
       <c r="F35" t="n">
-        <v>-3.463652883592532</v>
-      </c>
-      <c r="G35" t="inlineStr"/>
-      <c r="H35" t="n">
-        <v>-3.001880951613521</v>
-      </c>
-      <c r="I35" t="n">
-        <v>-3.44591734749921</v>
-      </c>
+        <v>-2.962753222493237</v>
+      </c>
+      <c r="G35" t="n">
+        <v>-0.690198438333234</v>
+      </c>
+      <c r="H35" t="inlineStr"/>
+      <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
+      <c r="K35" t="n">
+        <v>-2.117965233820735</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>C to V</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr"/>
-      <c r="C36" t="inlineStr"/>
-      <c r="D36" t="inlineStr"/>
+          <t>T to G</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>-1.824492557661394</v>
+      </c>
+      <c r="C36" t="n">
+        <v>-3.01544633523496</v>
+      </c>
+      <c r="D36" t="n">
+        <v>-3.025966020837576</v>
+      </c>
       <c r="E36" t="n">
-        <v>-3.206384370288202</v>
-      </c>
-      <c r="F36" t="inlineStr"/>
-      <c r="G36" t="inlineStr"/>
-      <c r="H36" t="inlineStr"/>
+        <v>-0.8123735133237393</v>
+      </c>
+      <c r="F36" t="n">
+        <v>-1.016908187940959</v>
+      </c>
+      <c r="G36" t="n">
+        <v>-2.037173842938715</v>
+      </c>
+      <c r="H36" t="n">
+        <v>-2.021652997820707</v>
+      </c>
       <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
+      <c r="J36" t="n">
+        <v>-1.60635625247893</v>
+      </c>
+      <c r="K36" t="n">
+        <v>-2.536178496201575</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>I to R</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr"/>
-      <c r="C37" t="inlineStr"/>
-      <c r="D37" t="inlineStr"/>
-      <c r="E37" t="inlineStr"/>
+          <t>A to V</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>-0.8384401961887611</v>
+      </c>
+      <c r="C37" t="n">
+        <v>-0.4625713977352778</v>
+      </c>
+      <c r="D37" t="n">
+        <v>-0.7377364482591892</v>
+      </c>
+      <c r="E37" t="n">
+        <v>-0.2492998169569994</v>
+      </c>
       <c r="F37" t="n">
-        <v>-2.145747766147483</v>
-      </c>
-      <c r="G37" t="inlineStr"/>
-      <c r="H37" t="inlineStr"/>
-      <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
+        <v>-0.7874788780152924</v>
+      </c>
+      <c r="G37" t="n">
+        <v>-1.130231168418733</v>
+      </c>
+      <c r="H37" t="n">
+        <v>-0.4314091091965606</v>
+      </c>
+      <c r="I37" t="n">
+        <v>-1.187371363352375</v>
+      </c>
+      <c r="J37" t="n">
+        <v>-0.8749139941855311</v>
+      </c>
       <c r="K37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>H to N</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr"/>
-      <c r="C38" t="inlineStr"/>
-      <c r="D38" t="inlineStr"/>
-      <c r="E38" t="n">
-        <v>-3.278180091207601</v>
-      </c>
+          <t>C to N</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>-0.4697583282615717</v>
+      </c>
+      <c r="C38" t="n">
+        <v>-0.5274370004573878</v>
+      </c>
+      <c r="D38" t="n">
+        <v>-0.4110655324338267</v>
+      </c>
+      <c r="E38" t="inlineStr"/>
       <c r="F38" t="n">
-        <v>-3.039534065436603</v>
+        <v>0.8927809093496122</v>
       </c>
       <c r="G38" t="inlineStr"/>
       <c r="H38" t="inlineStr"/>
@@ -1390,240 +1442,218 @@
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>A to E</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr"/>
-      <c r="C39" t="inlineStr"/>
-      <c r="D39" t="inlineStr"/>
-      <c r="E39" t="n">
-        <v>-1.456888424762672</v>
-      </c>
-      <c r="F39" t="inlineStr"/>
+          <t>T to Q</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>-3.335213433745747</v>
+      </c>
+      <c r="C39" t="n">
+        <v>-2.768728288937185</v>
+      </c>
+      <c r="D39" t="n">
+        <v>-2.516931923237659</v>
+      </c>
+      <c r="E39" t="inlineStr"/>
+      <c r="F39" t="n">
+        <v>-2.803814463433845</v>
+      </c>
       <c r="G39" t="inlineStr"/>
       <c r="H39" t="inlineStr"/>
-      <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
+      <c r="I39" t="n">
+        <v>-2.587503963480125</v>
+      </c>
+      <c r="J39" t="n">
+        <v>-2.22657270905446</v>
+      </c>
       <c r="K39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>W to D</t>
-        </is>
-      </c>
-      <c r="B40" t="n">
-        <v>-2.602685148274678</v>
-      </c>
+          <t>T to N</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr"/>
       <c r="C40" t="n">
-        <v>-2.62748630714627</v>
-      </c>
-      <c r="D40" t="n">
-        <v>-2.850291869728209</v>
-      </c>
+        <v>-0.8856825678462671</v>
+      </c>
+      <c r="D40" t="inlineStr"/>
       <c r="E40" t="n">
-        <v>-2.878491589677356</v>
-      </c>
-      <c r="F40" t="n">
-        <v>-3.030607253361953</v>
-      </c>
-      <c r="G40" t="n">
-        <v>-3.012956199531247</v>
-      </c>
+        <v>-0.9073352310048021</v>
+      </c>
+      <c r="F40" t="inlineStr"/>
+      <c r="G40" t="inlineStr"/>
       <c r="H40" t="inlineStr"/>
-      <c r="I40" t="n">
-        <v>-2.342985744786325</v>
-      </c>
+      <c r="I40" t="inlineStr"/>
       <c r="J40" t="inlineStr"/>
-      <c r="K40" t="n">
-        <v>-2.424437349119346</v>
-      </c>
+      <c r="K40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>M to T</t>
+          <t>Q to V</t>
         </is>
       </c>
       <c r="B41" t="inlineStr"/>
-      <c r="C41" t="n">
-        <v>-2.997671962076633</v>
-      </c>
+      <c r="C41" t="inlineStr"/>
       <c r="D41" t="inlineStr"/>
       <c r="E41" t="inlineStr"/>
-      <c r="F41" t="inlineStr"/>
-      <c r="G41" t="n">
-        <v>-2.897380778067156</v>
-      </c>
-      <c r="H41" t="n">
-        <v>-2.49346593273689</v>
-      </c>
-      <c r="I41" t="n">
-        <v>-2.143942079674241</v>
-      </c>
-      <c r="J41" t="n">
-        <v>-2.129683849273043</v>
-      </c>
-      <c r="K41" t="n">
-        <v>-2.802777599482629</v>
-      </c>
+      <c r="F41" t="n">
+        <v>2.000873105475007</v>
+      </c>
+      <c r="G41" t="inlineStr"/>
+      <c r="H41" t="inlineStr"/>
+      <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>L to V</t>
-        </is>
-      </c>
-      <c r="B42" t="n">
-        <v>-1.390571289949965</v>
-      </c>
-      <c r="C42" t="n">
-        <v>-1.669289288385584</v>
-      </c>
-      <c r="D42" t="n">
-        <v>-0.2927776990335118</v>
-      </c>
-      <c r="E42" t="n">
-        <v>0.1323515252243208</v>
-      </c>
-      <c r="F42" t="n">
-        <v>-0.3511144902211943</v>
-      </c>
-      <c r="G42" t="inlineStr"/>
-      <c r="H42" t="n">
-        <v>-0.5376451252399019</v>
-      </c>
-      <c r="I42" t="n">
-        <v>-0.1480074525387426</v>
-      </c>
-      <c r="J42" t="n">
-        <v>-2.02180069078898</v>
-      </c>
+          <t>Q to N</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr"/>
+      <c r="C42" t="inlineStr"/>
+      <c r="D42" t="inlineStr"/>
+      <c r="E42" t="inlineStr"/>
+      <c r="F42" t="inlineStr"/>
+      <c r="G42" t="n">
+        <v>-1.745148234545652</v>
+      </c>
+      <c r="H42" t="inlineStr"/>
+      <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
       <c r="K42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>P to N</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr"/>
+          <t>A to T</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>0.02875263253085487</v>
+      </c>
       <c r="C43" t="n">
-        <v>-0.9695580167104918</v>
+        <v>-0.4228200836303959</v>
       </c>
       <c r="D43" t="n">
-        <v>-1.664879863435469</v>
-      </c>
-      <c r="E43" t="inlineStr"/>
-      <c r="F43" t="inlineStr"/>
+        <v>-1.409847034239312</v>
+      </c>
+      <c r="E43" t="n">
+        <v>-0.04673617028414147</v>
+      </c>
+      <c r="F43" t="n">
+        <v>-0.1182077753621543</v>
+      </c>
       <c r="G43" t="inlineStr"/>
-      <c r="H43" t="n">
-        <v>-1.216538715227219</v>
-      </c>
+      <c r="H43" t="inlineStr"/>
       <c r="I43" t="inlineStr"/>
       <c r="J43" t="n">
-        <v>-0.4258995243360377</v>
-      </c>
-      <c r="K43" t="inlineStr"/>
+        <v>-1.376424251288294</v>
+      </c>
+      <c r="K43" t="n">
+        <v>-1.496902947068001</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>F to I/L</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr"/>
+          <t>A to P</t>
+        </is>
+      </c>
+      <c r="B44" t="n">
+        <v>-2.488326207050311</v>
+      </c>
       <c r="C44" t="n">
-        <v>0.6447831101546906</v>
+        <v>-2.453681036341224</v>
       </c>
       <c r="D44" t="n">
-        <v>-0.6931779928447728</v>
-      </c>
-      <c r="E44" t="n">
-        <v>-1.114381830490478</v>
-      </c>
-      <c r="F44" t="inlineStr"/>
+        <v>-2.425028502336098</v>
+      </c>
+      <c r="E44" t="inlineStr"/>
+      <c r="F44" t="n">
+        <v>-2.752703272375538</v>
+      </c>
       <c r="G44" t="n">
-        <v>-1.467761063278494</v>
+        <v>-2.549211859495849</v>
       </c>
       <c r="H44" t="inlineStr"/>
       <c r="I44" t="inlineStr"/>
-      <c r="J44" t="inlineStr"/>
+      <c r="J44" t="n">
+        <v>-2.580711409807245</v>
+      </c>
       <c r="K44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>Q to A</t>
+          <t>V to T</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>-0.3619759289519581</v>
-      </c>
-      <c r="C45" t="n">
-        <v>0.1069646733456389</v>
-      </c>
-      <c r="D45" t="n">
-        <v>-2.660431542968581</v>
-      </c>
-      <c r="E45" t="n">
-        <v>-1.61613884039599</v>
-      </c>
-      <c r="F45" t="n">
-        <v>0.009813389509508098</v>
-      </c>
-      <c r="G45" t="n">
-        <v>-0.626884783722778</v>
-      </c>
+        <v>-2.381487207945247</v>
+      </c>
+      <c r="C45" t="inlineStr"/>
+      <c r="D45" t="inlineStr"/>
+      <c r="E45" t="inlineStr"/>
+      <c r="F45" t="inlineStr"/>
+      <c r="G45" t="inlineStr"/>
       <c r="H45" t="n">
-        <v>-1.271921085739113</v>
+        <v>-1.438918787536255</v>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="J45" t="n">
-        <v>0.763254670072101</v>
+        <v>-1.945923322388674</v>
       </c>
       <c r="K45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>F to M</t>
+          <t>N to S</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>-1.252480097425043</v>
-      </c>
-      <c r="C46" t="inlineStr"/>
-      <c r="D46" t="inlineStr"/>
-      <c r="E46" t="inlineStr"/>
+        <v>-1.220899976660314</v>
+      </c>
+      <c r="C46" t="n">
+        <v>-2.051238538092127</v>
+      </c>
+      <c r="D46" t="n">
+        <v>-1.767355338190012</v>
+      </c>
+      <c r="E46" t="n">
+        <v>-0.8687846315630907</v>
+      </c>
       <c r="F46" t="inlineStr"/>
-      <c r="G46" t="inlineStr"/>
+      <c r="G46" t="n">
+        <v>-1.351173262866905</v>
+      </c>
       <c r="H46" t="inlineStr"/>
       <c r="I46" t="inlineStr"/>
-      <c r="J46" t="inlineStr"/>
-      <c r="K46" t="inlineStr"/>
+      <c r="J46" t="n">
+        <v>-1.591116997728084</v>
+      </c>
+      <c r="K46" t="n">
+        <v>-1.253467642702373</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>G to T</t>
+          <t>F to V</t>
         </is>
       </c>
       <c r="B47" t="inlineStr"/>
-      <c r="C47" t="n">
-        <v>-2.951949805290317</v>
-      </c>
-      <c r="D47" t="n">
-        <v>-2.750847923132405</v>
-      </c>
-      <c r="E47" t="n">
-        <v>-2.953556297972268</v>
-      </c>
-      <c r="F47" t="n">
-        <v>-2.715215769917584</v>
-      </c>
+      <c r="C47" t="inlineStr"/>
+      <c r="D47" t="inlineStr"/>
+      <c r="E47" t="inlineStr"/>
+      <c r="F47" t="inlineStr"/>
       <c r="G47" t="n">
-        <v>-3.156109793212363</v>
+        <v>-1.810759626831118</v>
       </c>
       <c r="H47" t="inlineStr"/>
       <c r="I47" t="inlineStr"/>
@@ -1633,144 +1663,116 @@
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>T to A</t>
-        </is>
-      </c>
-      <c r="B48" t="n">
-        <v>0.6158106322651906</v>
-      </c>
-      <c r="C48" t="n">
-        <v>0.5631040646903495</v>
-      </c>
+          <t>G to N</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr"/>
+      <c r="C48" t="inlineStr"/>
       <c r="D48" t="n">
-        <v>-0.05873273195186385</v>
-      </c>
-      <c r="E48" t="n">
-        <v>-0.3882789170631177</v>
-      </c>
-      <c r="F48" t="n">
-        <v>-0.4779700911410305</v>
-      </c>
+        <v>-2.752132297722793</v>
+      </c>
+      <c r="E48" t="inlineStr"/>
+      <c r="F48" t="inlineStr"/>
       <c r="G48" t="inlineStr"/>
-      <c r="H48" t="n">
-        <v>0.0501144684486006</v>
-      </c>
+      <c r="H48" t="inlineStr"/>
       <c r="I48" t="n">
-        <v>0.8457255883973716</v>
+        <v>-2.52309259852472</v>
       </c>
       <c r="J48" t="n">
-        <v>-0.0316255295385095</v>
-      </c>
-      <c r="K48" t="n">
-        <v>-1.189264442513201</v>
-      </c>
+        <v>-1.7208880406526</v>
+      </c>
+      <c r="K48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>W to S</t>
-        </is>
-      </c>
-      <c r="B49" t="n">
-        <v>-2.433354501560562</v>
-      </c>
-      <c r="C49" t="n">
-        <v>-2.197809391453416</v>
-      </c>
-      <c r="D49" t="n">
-        <v>-2.688055575218811</v>
-      </c>
+          <t>Q to P</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr"/>
+      <c r="C49" t="inlineStr"/>
+      <c r="D49" t="inlineStr"/>
       <c r="E49" t="n">
-        <v>-2.260979225408565</v>
-      </c>
-      <c r="F49" t="n">
-        <v>-3.01459567260336</v>
-      </c>
-      <c r="G49" t="n">
-        <v>-2.354252076144672</v>
-      </c>
-      <c r="H49" t="n">
-        <v>-2.60012179261971</v>
-      </c>
+        <v>0.01996122983687781</v>
+      </c>
+      <c r="F49" t="inlineStr"/>
+      <c r="G49" t="inlineStr"/>
+      <c r="H49" t="inlineStr"/>
       <c r="I49" t="inlineStr"/>
-      <c r="J49" t="n">
-        <v>-2.182769764986223</v>
-      </c>
+      <c r="J49" t="inlineStr"/>
       <c r="K49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>C to G</t>
-        </is>
-      </c>
-      <c r="B50" t="n">
-        <v>-1.604583302921172</v>
-      </c>
+          <t>L to S</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr"/>
       <c r="C50" t="n">
-        <v>-1.653379736453924</v>
+        <v>-3.303445692792092</v>
       </c>
       <c r="D50" t="n">
-        <v>-1.650305588338055</v>
+        <v>-3.543628069658578</v>
       </c>
       <c r="E50" t="n">
-        <v>-1.498145046900468</v>
+        <v>-3.67230027388256</v>
       </c>
       <c r="F50" t="n">
-        <v>-1.429114256626512</v>
-      </c>
-      <c r="G50" t="inlineStr"/>
+        <v>-3.575121950461244</v>
+      </c>
+      <c r="G50" t="n">
+        <v>-3.422816315225209</v>
+      </c>
       <c r="H50" t="inlineStr"/>
       <c r="I50" t="inlineStr"/>
-      <c r="J50" t="inlineStr"/>
+      <c r="J50" t="n">
+        <v>-3.318062107134399</v>
+      </c>
       <c r="K50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
         <is>
-          <t>T to I/L</t>
+          <t>A to E</t>
         </is>
       </c>
       <c r="B51" t="inlineStr"/>
       <c r="C51" t="inlineStr"/>
       <c r="D51" t="inlineStr"/>
-      <c r="E51" t="inlineStr"/>
+      <c r="E51" t="n">
+        <v>-1.456888424762672</v>
+      </c>
       <c r="F51" t="inlineStr"/>
       <c r="G51" t="inlineStr"/>
       <c r="H51" t="inlineStr"/>
       <c r="I51" t="inlineStr"/>
-      <c r="J51" t="n">
-        <v>1.945140599196265</v>
-      </c>
+      <c r="J51" t="inlineStr"/>
       <c r="K51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
         <is>
-          <t>P to A</t>
-        </is>
-      </c>
-      <c r="B52" t="n">
-        <v>-1.865159710553465</v>
-      </c>
+          <t>G to T</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr"/>
       <c r="C52" t="n">
-        <v>-0.8853371665991663</v>
+        <v>-2.951949805290317</v>
       </c>
       <c r="D52" t="n">
-        <v>-1.354458591812705</v>
+        <v>-2.750847923132405</v>
       </c>
       <c r="E52" t="n">
-        <v>-1.797264822207178</v>
+        <v>-2.953556297972268</v>
       </c>
       <c r="F52" t="n">
-        <v>-0.08751827316426125</v>
+        <v>-2.715215769917584</v>
       </c>
       <c r="G52" t="n">
-        <v>-0.04723405743084132</v>
-      </c>
-      <c r="H52" t="n">
-        <v>0.4707840653703282</v>
-      </c>
+        <v>-3.156109793212363</v>
+      </c>
+      <c r="H52" t="inlineStr"/>
       <c r="I52" t="inlineStr"/>
       <c r="J52" t="inlineStr"/>
       <c r="K52" t="inlineStr"/>
@@ -1778,188 +1780,170 @@
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
         <is>
-          <t>D to M</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr"/>
+          <t>G to S</t>
+        </is>
+      </c>
+      <c r="B53" t="n">
+        <v>-1.745077699105976</v>
+      </c>
       <c r="C53" t="n">
-        <v>-1.708101373184544</v>
+        <v>-1.866754888350168</v>
       </c>
       <c r="D53" t="n">
-        <v>0.6947551869677342</v>
+        <v>-2.080123011830736</v>
       </c>
       <c r="E53" t="n">
-        <v>-1.257065657302828</v>
+        <v>0.02179676844025173</v>
       </c>
       <c r="F53" t="n">
-        <v>-1.053772409055846</v>
-      </c>
-      <c r="G53" t="inlineStr"/>
+        <v>-1.142756069897438</v>
+      </c>
+      <c r="G53" t="n">
+        <v>-0.1318026355199155</v>
+      </c>
       <c r="H53" t="inlineStr"/>
       <c r="I53" t="inlineStr"/>
-      <c r="J53" t="inlineStr"/>
+      <c r="J53" t="n">
+        <v>-2.014333161287967</v>
+      </c>
       <c r="K53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="1" t="inlineStr">
         <is>
-          <t>G to E</t>
-        </is>
-      </c>
-      <c r="B54" t="n">
-        <v>-1.633234393323919</v>
-      </c>
+          <t>F to I/L</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr"/>
       <c r="C54" t="n">
-        <v>-4.352484278919642</v>
+        <v>0.6447831101546906</v>
       </c>
       <c r="D54" t="n">
-        <v>-1.78837510805909</v>
+        <v>-0.6931779928447728</v>
       </c>
       <c r="E54" t="n">
-        <v>-1.396171682236512</v>
-      </c>
-      <c r="F54" t="n">
-        <v>-1.591203784988571</v>
-      </c>
-      <c r="G54" t="inlineStr"/>
+        <v>-1.114381830490478</v>
+      </c>
+      <c r="F54" t="inlineStr"/>
+      <c r="G54" t="n">
+        <v>-1.467761063278494</v>
+      </c>
       <c r="H54" t="inlineStr"/>
-      <c r="I54" t="n">
-        <v>-1.055060075300377</v>
-      </c>
+      <c r="I54" t="inlineStr"/>
       <c r="J54" t="inlineStr"/>
       <c r="K54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="1" t="inlineStr">
         <is>
-          <t>P to T</t>
-        </is>
-      </c>
-      <c r="B55" t="n">
-        <v>-1.378795339808385</v>
-      </c>
-      <c r="C55" t="n">
-        <v>-1.388568315633956</v>
-      </c>
-      <c r="D55" t="n">
-        <v>-1.856271864209096</v>
-      </c>
-      <c r="E55" t="n">
-        <v>-1.644315982108478</v>
-      </c>
+          <t>F to P</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr"/>
+      <c r="C55" t="inlineStr"/>
+      <c r="D55" t="inlineStr"/>
+      <c r="E55" t="inlineStr"/>
       <c r="F55" t="n">
-        <v>-1.774377006173016</v>
-      </c>
-      <c r="G55" t="n">
-        <v>-0.4833337585628716</v>
-      </c>
-      <c r="H55" t="n">
-        <v>-1.26882658524452</v>
-      </c>
-      <c r="I55" t="n">
-        <v>-1.333824698279085</v>
-      </c>
-      <c r="J55" t="n">
-        <v>-1.669105188879012</v>
-      </c>
-      <c r="K55" t="n">
-        <v>-0.652745001026258</v>
-      </c>
+        <v>-1.982962899156609</v>
+      </c>
+      <c r="G55" t="inlineStr"/>
+      <c r="H55" t="inlineStr"/>
+      <c r="I55" t="inlineStr"/>
+      <c r="J55" t="inlineStr"/>
+      <c r="K55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
         <is>
-          <t>L to M</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr"/>
+          <t>A to G</t>
+        </is>
+      </c>
+      <c r="B56" t="n">
+        <v>-0.5317275257810317</v>
+      </c>
       <c r="C56" t="n">
-        <v>-0.8374896289325378</v>
-      </c>
-      <c r="D56" t="inlineStr"/>
-      <c r="E56" t="n">
-        <v>-1.778352863980573</v>
-      </c>
-      <c r="F56" t="inlineStr"/>
+        <v>-3.202684684370035</v>
+      </c>
+      <c r="D56" t="n">
+        <v>-2.165109501332983</v>
+      </c>
+      <c r="E56" t="inlineStr"/>
+      <c r="F56" t="n">
+        <v>-2.755936204476399</v>
+      </c>
       <c r="G56" t="inlineStr"/>
       <c r="H56" t="inlineStr"/>
       <c r="I56" t="inlineStr"/>
       <c r="J56" t="inlineStr"/>
-      <c r="K56" t="inlineStr"/>
+      <c r="K56" t="n">
+        <v>-2.230254087621095</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="inlineStr">
         <is>
-          <t>V to I/L</t>
+          <t>G to E</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>-0.01766140843393098</v>
+        <v>-1.633234393323919</v>
       </c>
       <c r="C57" t="n">
-        <v>0.03107672106072522</v>
+        <v>-4.352484278919642</v>
       </c>
       <c r="D57" t="n">
-        <v>0.1900077366633942</v>
+        <v>-1.78837510805909</v>
       </c>
       <c r="E57" t="n">
-        <v>-1.338706592904841</v>
+        <v>-1.396171682236512</v>
       </c>
       <c r="F57" t="n">
-        <v>0.3464496316642493</v>
-      </c>
-      <c r="G57" t="n">
-        <v>0.2434189947951148</v>
-      </c>
+        <v>-1.591203784988571</v>
+      </c>
+      <c r="G57" t="inlineStr"/>
       <c r="H57" t="inlineStr"/>
       <c r="I57" t="n">
-        <v>-0.3253046634918442</v>
-      </c>
-      <c r="J57" t="n">
-        <v>0.03609218343390806</v>
-      </c>
+        <v>-1.055060075300377</v>
+      </c>
+      <c r="J57" t="inlineStr"/>
       <c r="K57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="1" t="inlineStr">
         <is>
-          <t>R to F</t>
+          <t>G to A</t>
         </is>
       </c>
       <c r="B58" t="inlineStr"/>
-      <c r="C58" t="inlineStr"/>
-      <c r="D58" t="inlineStr"/>
+      <c r="C58" t="n">
+        <v>-0.1823659777842622</v>
+      </c>
+      <c r="D58" t="n">
+        <v>-2.730527398715791</v>
+      </c>
       <c r="E58" t="inlineStr"/>
-      <c r="F58" t="n">
-        <v>-2.494653312636166</v>
-      </c>
+      <c r="F58" t="inlineStr"/>
       <c r="G58" t="inlineStr"/>
       <c r="H58" t="inlineStr"/>
-      <c r="I58" t="inlineStr"/>
-      <c r="J58" t="n">
-        <v>-1.990583297831177</v>
-      </c>
+      <c r="I58" t="n">
+        <v>-0.1214902790354423</v>
+      </c>
+      <c r="J58" t="inlineStr"/>
       <c r="K58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="1" t="inlineStr">
         <is>
-          <t>C to N</t>
+          <t>F to M</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>-0.4697583282615717</v>
-      </c>
-      <c r="C59" t="n">
-        <v>-0.5274370004573878</v>
-      </c>
-      <c r="D59" t="n">
-        <v>-0.4110655324338267</v>
-      </c>
+        <v>-1.252480097425043</v>
+      </c>
+      <c r="C59" t="inlineStr"/>
+      <c r="D59" t="inlineStr"/>
       <c r="E59" t="inlineStr"/>
-      <c r="F59" t="n">
-        <v>0.8927809093496122</v>
-      </c>
+      <c r="F59" t="inlineStr"/>
       <c r="G59" t="inlineStr"/>
       <c r="H59" t="inlineStr"/>
       <c r="I59" t="inlineStr"/>
@@ -1969,75 +1953,59 @@
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
         <is>
-          <t>C to S</t>
-        </is>
-      </c>
-      <c r="B60" t="inlineStr"/>
+          <t>I to T</t>
+        </is>
+      </c>
+      <c r="B60" t="n">
+        <v>2.315423482620839</v>
+      </c>
       <c r="C60" t="n">
-        <v>-1.844028167018038</v>
+        <v>-3.117670437503977</v>
       </c>
       <c r="D60" t="inlineStr"/>
-      <c r="E60" t="n">
-        <v>0.2475281446492634</v>
-      </c>
+      <c r="E60" t="inlineStr"/>
       <c r="F60" t="inlineStr"/>
-      <c r="G60" t="n">
-        <v>-0.9407052210779292</v>
-      </c>
+      <c r="G60" t="inlineStr"/>
       <c r="H60" t="inlineStr"/>
       <c r="I60" t="inlineStr"/>
-      <c r="J60" t="inlineStr"/>
+      <c r="J60" t="n">
+        <v>-2.418029242897276</v>
+      </c>
       <c r="K60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="1" t="inlineStr">
         <is>
-          <t>I to V</t>
+          <t>L to P</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>0.2964127259572112</v>
-      </c>
-      <c r="C61" t="n">
-        <v>-0.3204300206009085</v>
-      </c>
-      <c r="D61" t="n">
-        <v>-0.2853090975187899</v>
-      </c>
-      <c r="E61" t="n">
-        <v>0.1675091654826392</v>
-      </c>
-      <c r="F61" t="n">
-        <v>-0.3529848185555949</v>
-      </c>
-      <c r="G61" t="n">
-        <v>-0.2201549293866399</v>
-      </c>
-      <c r="H61" t="n">
-        <v>-1.794348501532178</v>
-      </c>
+        <v>0.03979614585522858</v>
+      </c>
+      <c r="C61" t="inlineStr"/>
+      <c r="D61" t="inlineStr"/>
+      <c r="E61" t="inlineStr"/>
+      <c r="F61" t="inlineStr"/>
+      <c r="G61" t="inlineStr"/>
+      <c r="H61" t="inlineStr"/>
       <c r="I61" t="inlineStr"/>
-      <c r="J61" t="n">
-        <v>-1.025394863591695</v>
-      </c>
-      <c r="K61" t="n">
-        <v>-1.234195473178331</v>
-      </c>
+      <c r="J61" t="inlineStr"/>
+      <c r="K61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="1" t="inlineStr">
         <is>
-          <t>Q to N</t>
+          <t>V to G</t>
         </is>
       </c>
       <c r="B62" t="inlineStr"/>
       <c r="C62" t="inlineStr"/>
-      <c r="D62" t="inlineStr"/>
+      <c r="D62" t="n">
+        <v>-2.953212148393054</v>
+      </c>
       <c r="E62" t="inlineStr"/>
       <c r="F62" t="inlineStr"/>
-      <c r="G62" t="n">
-        <v>-1.745148234545652</v>
-      </c>
+      <c r="G62" t="inlineStr"/>
       <c r="H62" t="inlineStr"/>
       <c r="I62" t="inlineStr"/>
       <c r="J62" t="inlineStr"/>
@@ -2046,42 +2014,36 @@
     <row r="63">
       <c r="A63" s="1" t="inlineStr">
         <is>
-          <t>G to N</t>
-        </is>
-      </c>
-      <c r="B63" t="inlineStr"/>
+          <t>E to M</t>
+        </is>
+      </c>
+      <c r="B63" t="n">
+        <v>-1.287044195139228</v>
+      </c>
       <c r="C63" t="inlineStr"/>
-      <c r="D63" t="n">
-        <v>-2.752132297722793</v>
-      </c>
+      <c r="D63" t="inlineStr"/>
       <c r="E63" t="inlineStr"/>
       <c r="F63" t="inlineStr"/>
       <c r="G63" t="inlineStr"/>
       <c r="H63" t="inlineStr"/>
-      <c r="I63" t="n">
-        <v>-2.52309259852472</v>
-      </c>
-      <c r="J63" t="n">
-        <v>-1.7208880406526</v>
-      </c>
+      <c r="I63" t="inlineStr"/>
+      <c r="J63" t="inlineStr"/>
       <c r="K63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="1" t="inlineStr">
         <is>
-          <t>M to I/L</t>
+          <t>N to W</t>
         </is>
       </c>
       <c r="B64" t="inlineStr"/>
       <c r="C64" t="inlineStr"/>
-      <c r="D64" t="n">
-        <v>-0.08440509815701522</v>
-      </c>
+      <c r="D64" t="inlineStr"/>
       <c r="E64" t="inlineStr"/>
-      <c r="F64" t="n">
-        <v>0.01961211254722646</v>
-      </c>
-      <c r="G64" t="inlineStr"/>
+      <c r="F64" t="inlineStr"/>
+      <c r="G64" t="n">
+        <v>-2.099940029042119</v>
+      </c>
       <c r="H64" t="inlineStr"/>
       <c r="I64" t="inlineStr"/>
       <c r="J64" t="inlineStr"/>
@@ -2090,35 +2052,43 @@
     <row r="65">
       <c r="A65" s="1" t="inlineStr">
         <is>
-          <t>L to P</t>
-        </is>
-      </c>
-      <c r="B65" t="n">
-        <v>0.03979614585522858</v>
-      </c>
-      <c r="C65" t="inlineStr"/>
-      <c r="D65" t="inlineStr"/>
+          <t>P to N</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr"/>
+      <c r="C65" t="n">
+        <v>-0.9695580167104918</v>
+      </c>
+      <c r="D65" t="n">
+        <v>-1.664879863435469</v>
+      </c>
       <c r="E65" t="inlineStr"/>
       <c r="F65" t="inlineStr"/>
       <c r="G65" t="inlineStr"/>
-      <c r="H65" t="inlineStr"/>
+      <c r="H65" t="n">
+        <v>-1.216538715227219</v>
+      </c>
       <c r="I65" t="inlineStr"/>
-      <c r="J65" t="inlineStr"/>
+      <c r="J65" t="n">
+        <v>-0.4258995243360377</v>
+      </c>
       <c r="K65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="1" t="inlineStr">
         <is>
-          <t>C to I/L</t>
+          <t>M to G</t>
         </is>
       </c>
       <c r="B66" t="inlineStr"/>
-      <c r="C66" t="n">
-        <v>-0.2614433172230166</v>
-      </c>
+      <c r="C66" t="inlineStr"/>
       <c r="D66" t="inlineStr"/>
-      <c r="E66" t="inlineStr"/>
-      <c r="F66" t="inlineStr"/>
+      <c r="E66" t="n">
+        <v>-1.506132862323145</v>
+      </c>
+      <c r="F66" t="n">
+        <v>-2.073913401043293</v>
+      </c>
       <c r="G66" t="inlineStr"/>
       <c r="H66" t="inlineStr"/>
       <c r="I66" t="inlineStr"/>
@@ -2128,123 +2098,125 @@
     <row r="67">
       <c r="A67" s="1" t="inlineStr">
         <is>
-          <t>N to W</t>
-        </is>
-      </c>
-      <c r="B67" t="inlineStr"/>
-      <c r="C67" t="inlineStr"/>
-      <c r="D67" t="inlineStr"/>
-      <c r="E67" t="inlineStr"/>
-      <c r="F67" t="inlineStr"/>
-      <c r="G67" t="n">
-        <v>-2.099940029042119</v>
-      </c>
+          <t>M to D</t>
+        </is>
+      </c>
+      <c r="B67" t="n">
+        <v>-2.979197817339391</v>
+      </c>
+      <c r="C67" t="n">
+        <v>-2.36465280004258</v>
+      </c>
+      <c r="D67" t="n">
+        <v>-2.754280781271393</v>
+      </c>
+      <c r="E67" t="n">
+        <v>-3.12422646429992</v>
+      </c>
+      <c r="F67" t="n">
+        <v>-1.888920356329621</v>
+      </c>
+      <c r="G67" t="inlineStr"/>
       <c r="H67" t="inlineStr"/>
       <c r="I67" t="inlineStr"/>
-      <c r="J67" t="inlineStr"/>
+      <c r="J67" t="n">
+        <v>-2.876351306287587</v>
+      </c>
       <c r="K67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="1" t="inlineStr">
         <is>
-          <t>T to Q</t>
-        </is>
-      </c>
-      <c r="B68" t="n">
-        <v>-3.335213433745747</v>
-      </c>
-      <c r="C68" t="n">
-        <v>-2.768728288937185</v>
-      </c>
-      <c r="D68" t="n">
-        <v>-2.516931923237659</v>
-      </c>
-      <c r="E68" t="inlineStr"/>
+          <t>E to N</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr"/>
+      <c r="C68" t="inlineStr"/>
+      <c r="D68" t="inlineStr"/>
+      <c r="E68" t="n">
+        <v>-1.050732675513399</v>
+      </c>
       <c r="F68" t="n">
-        <v>-2.803814463433845</v>
-      </c>
-      <c r="G68" t="inlineStr"/>
+        <v>-1.747000236646142</v>
+      </c>
+      <c r="G68" t="n">
+        <v>-1.611690933862995</v>
+      </c>
       <c r="H68" t="inlineStr"/>
-      <c r="I68" t="n">
-        <v>-2.587503963480125</v>
-      </c>
-      <c r="J68" t="n">
-        <v>-2.22657270905446</v>
-      </c>
+      <c r="I68" t="inlineStr"/>
+      <c r="J68" t="inlineStr"/>
       <c r="K68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="1" t="inlineStr">
         <is>
-          <t>V to Q</t>
-        </is>
-      </c>
-      <c r="B69" t="inlineStr"/>
-      <c r="C69" t="inlineStr"/>
-      <c r="D69" t="inlineStr"/>
+          <t>M to V</t>
+        </is>
+      </c>
+      <c r="B69" t="n">
+        <v>-0.2241391488972727</v>
+      </c>
+      <c r="C69" t="n">
+        <v>-1.281438780384316</v>
+      </c>
+      <c r="D69" t="n">
+        <v>-2.562784537507083</v>
+      </c>
       <c r="E69" t="inlineStr"/>
-      <c r="F69" t="inlineStr"/>
+      <c r="F69" t="n">
+        <v>-1.714215125015041</v>
+      </c>
       <c r="G69" t="n">
-        <v>-1.557785451729937</v>
+        <v>-1.612589937679346</v>
       </c>
       <c r="H69" t="inlineStr"/>
       <c r="I69" t="inlineStr"/>
-      <c r="J69" t="inlineStr"/>
+      <c r="J69" t="n">
+        <v>0.1066627319573099</v>
+      </c>
       <c r="K69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="1" t="inlineStr">
         <is>
-          <t>V to A</t>
-        </is>
-      </c>
-      <c r="B70" t="n">
-        <v>-0.8072930572314686</v>
-      </c>
-      <c r="C70" t="n">
-        <v>0.01355251416744737</v>
-      </c>
-      <c r="D70" t="n">
-        <v>2.071131702541749</v>
-      </c>
-      <c r="E70" t="n">
-        <v>-1.858940607856459</v>
-      </c>
-      <c r="F70" t="n">
-        <v>-0.2921806432411803</v>
-      </c>
-      <c r="G70" t="n">
-        <v>0.5994838204215935</v>
-      </c>
+          <t>A to D</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr"/>
+      <c r="C70" t="inlineStr"/>
+      <c r="D70" t="inlineStr"/>
+      <c r="E70" t="inlineStr"/>
+      <c r="F70" t="inlineStr"/>
+      <c r="G70" t="inlineStr"/>
       <c r="H70" t="n">
-        <v>0.07325158936121866</v>
+        <v>-0.5675460116554798</v>
       </c>
       <c r="I70" t="n">
-        <v>0.5272452090096513</v>
+        <v>-1.235863259318905</v>
       </c>
       <c r="J70" t="n">
-        <v>-1.278681972903824</v>
+        <v>-1.48745941186576</v>
       </c>
       <c r="K70" t="n">
-        <v>1.341952077388964</v>
+        <v>0.2961007189974759</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="inlineStr">
         <is>
-          <t>Q to S</t>
-        </is>
-      </c>
-      <c r="B71" t="n">
-        <v>-1.790193560975912</v>
-      </c>
+          <t>V to D</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr"/>
       <c r="C71" t="inlineStr"/>
       <c r="D71" t="n">
-        <v>-1.879743654261167</v>
+        <v>-2.369744228178009</v>
       </c>
       <c r="E71" t="inlineStr"/>
       <c r="F71" t="inlineStr"/>
-      <c r="G71" t="inlineStr"/>
+      <c r="G71" t="n">
+        <v>-2.741604498435132</v>
+      </c>
       <c r="H71" t="inlineStr"/>
       <c r="I71" t="inlineStr"/>
       <c r="J71" t="inlineStr"/>
@@ -2253,116 +2225,126 @@
     <row r="72">
       <c r="A72" s="1" t="inlineStr">
         <is>
-          <t>N to G</t>
+          <t>G to Q</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>0.2455867936048637</v>
+        <v>-2.332913290549719</v>
       </c>
       <c r="C72" t="n">
-        <v>0.4723812007208647</v>
+        <v>-2.851837270175408</v>
       </c>
       <c r="D72" t="n">
-        <v>0.2173102315554214</v>
+        <v>-2.8355823200199</v>
       </c>
       <c r="E72" t="n">
-        <v>0.1349289281510108</v>
+        <v>-2.434241835029978</v>
       </c>
       <c r="F72" t="n">
-        <v>-2.263268897168105</v>
-      </c>
-      <c r="G72" t="inlineStr"/>
-      <c r="H72" t="inlineStr"/>
+        <v>-2.499741892092826</v>
+      </c>
+      <c r="G72" t="n">
+        <v>-2.31814227672377</v>
+      </c>
+      <c r="H72" t="n">
+        <v>-2.073985146743326</v>
+      </c>
       <c r="I72" t="inlineStr"/>
-      <c r="J72" t="inlineStr"/>
-      <c r="K72" t="n">
-        <v>0.2670062506797746</v>
-      </c>
+      <c r="J72" t="n">
+        <v>-2.949282404433042</v>
+      </c>
+      <c r="K72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="1" t="inlineStr">
         <is>
-          <t>E to M</t>
+          <t>N to G</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>-1.287044195139228</v>
-      </c>
-      <c r="C73" t="inlineStr"/>
-      <c r="D73" t="inlineStr"/>
-      <c r="E73" t="inlineStr"/>
-      <c r="F73" t="inlineStr"/>
+        <v>0.2455867936048637</v>
+      </c>
+      <c r="C73" t="n">
+        <v>0.4723812007208647</v>
+      </c>
+      <c r="D73" t="n">
+        <v>0.2173102315554214</v>
+      </c>
+      <c r="E73" t="n">
+        <v>0.1349289281510108</v>
+      </c>
+      <c r="F73" t="n">
+        <v>-2.263268897168105</v>
+      </c>
       <c r="G73" t="inlineStr"/>
       <c r="H73" t="inlineStr"/>
       <c r="I73" t="inlineStr"/>
       <c r="J73" t="inlineStr"/>
-      <c r="K73" t="inlineStr"/>
+      <c r="K73" t="n">
+        <v>0.2670062506797746</v>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="inlineStr">
         <is>
-          <t>A to Q</t>
+          <t>H to D</t>
         </is>
       </c>
       <c r="B74" t="inlineStr"/>
       <c r="C74" t="inlineStr"/>
       <c r="D74" t="inlineStr"/>
-      <c r="E74" t="n">
-        <v>-2.274948617468515</v>
-      </c>
-      <c r="F74" t="inlineStr"/>
-      <c r="G74" t="n">
-        <v>-2.328055224162954</v>
-      </c>
+      <c r="E74" t="inlineStr"/>
+      <c r="F74" t="n">
+        <v>-1.861486441134107</v>
+      </c>
+      <c r="G74" t="inlineStr"/>
       <c r="H74" t="inlineStr"/>
-      <c r="I74" t="n">
-        <v>-1.952558442403316</v>
-      </c>
-      <c r="J74" t="inlineStr"/>
+      <c r="I74" t="inlineStr"/>
+      <c r="J74" t="n">
+        <v>-1.932831549924681</v>
+      </c>
       <c r="K74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" s="1" t="inlineStr">
         <is>
-          <t>A to P</t>
+          <t>E to D</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>-2.488326207050311</v>
+        <v>-0.4225199078514148</v>
       </c>
       <c r="C75" t="n">
-        <v>-2.453681036341224</v>
+        <v>-0.2674458955549505</v>
       </c>
       <c r="D75" t="n">
-        <v>-2.425028502336098</v>
+        <v>-1.966506052238806</v>
       </c>
       <c r="E75" t="inlineStr"/>
       <c r="F75" t="n">
-        <v>-2.752703272375538</v>
+        <v>-0.3294074970866585</v>
       </c>
       <c r="G75" t="n">
-        <v>-2.549211859495849</v>
+        <v>0.04646614880749206</v>
       </c>
       <c r="H75" t="inlineStr"/>
       <c r="I75" t="inlineStr"/>
-      <c r="J75" t="n">
-        <v>-2.580711409807245</v>
-      </c>
+      <c r="J75" t="inlineStr"/>
       <c r="K75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="1" t="inlineStr">
         <is>
-          <t>E to G</t>
-        </is>
-      </c>
-      <c r="B76" t="n">
-        <v>-2.88830992385652</v>
-      </c>
+          <t>I to R</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr"/>
       <c r="C76" t="inlineStr"/>
       <c r="D76" t="inlineStr"/>
       <c r="E76" t="inlineStr"/>
-      <c r="F76" t="inlineStr"/>
+      <c r="F76" t="n">
+        <v>-2.145747766147483</v>
+      </c>
       <c r="G76" t="inlineStr"/>
       <c r="H76" t="inlineStr"/>
       <c r="I76" t="inlineStr"/>
@@ -2372,109 +2354,99 @@
     <row r="77">
       <c r="A77" s="1" t="inlineStr">
         <is>
-          <t>T to D</t>
+          <t>L to V</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>-2.708323957439661</v>
+        <v>-1.390571289949965</v>
       </c>
       <c r="C77" t="n">
-        <v>-2.313812233553072</v>
+        <v>-1.669289288385584</v>
       </c>
       <c r="D77" t="n">
-        <v>-2.991903582271612</v>
+        <v>-0.2927776990335118</v>
       </c>
       <c r="E77" t="n">
-        <v>-2.323665623467106</v>
+        <v>0.1323515252243208</v>
       </c>
       <c r="F77" t="n">
-        <v>-2.693899350223147</v>
-      </c>
-      <c r="G77" t="n">
-        <v>-2.006419287849925</v>
-      </c>
+        <v>-0.3511144902211943</v>
+      </c>
+      <c r="G77" t="inlineStr"/>
       <c r="H77" t="n">
-        <v>-2.302819058631381</v>
-      </c>
-      <c r="I77" t="inlineStr"/>
+        <v>-0.5376451252399019</v>
+      </c>
+      <c r="I77" t="n">
+        <v>-0.1480074525387426</v>
+      </c>
       <c r="J77" t="n">
-        <v>-2.297724439443744</v>
-      </c>
-      <c r="K77" t="n">
-        <v>-1.141653233714327</v>
-      </c>
+        <v>-2.02180069078898</v>
+      </c>
+      <c r="K77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="1" t="inlineStr">
         <is>
-          <t>T to S</t>
-        </is>
-      </c>
-      <c r="B78" t="inlineStr"/>
+          <t>W to D</t>
+        </is>
+      </c>
+      <c r="B78" t="n">
+        <v>-2.602685148274678</v>
+      </c>
       <c r="C78" t="n">
-        <v>-1.295784631214332</v>
+        <v>-2.62748630714627</v>
       </c>
       <c r="D78" t="n">
-        <v>-0.3115495110783237</v>
+        <v>-2.850291869728209</v>
       </c>
       <c r="E78" t="n">
-        <v>-0.2967358405509591</v>
+        <v>-2.878491589677356</v>
       </c>
       <c r="F78" t="n">
-        <v>-1.772160073286773</v>
+        <v>-3.030607253361953</v>
       </c>
       <c r="G78" t="n">
-        <v>-2.793307424141744</v>
-      </c>
-      <c r="H78" t="n">
-        <v>-0.6617959991633851</v>
-      </c>
-      <c r="I78" t="inlineStr"/>
+        <v>-3.012956199531247</v>
+      </c>
+      <c r="H78" t="inlineStr"/>
+      <c r="I78" t="n">
+        <v>-2.342985744786325</v>
+      </c>
       <c r="J78" t="inlineStr"/>
-      <c r="K78" t="inlineStr"/>
+      <c r="K78" t="n">
+        <v>-2.424437349119346</v>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="1" t="inlineStr">
         <is>
-          <t>M to D</t>
+          <t>C to A</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>-2.979197817339391</v>
-      </c>
-      <c r="C79" t="n">
-        <v>-2.36465280004258</v>
-      </c>
-      <c r="D79" t="n">
-        <v>-2.754280781271393</v>
-      </c>
-      <c r="E79" t="n">
-        <v>-3.12422646429992</v>
-      </c>
-      <c r="F79" t="n">
-        <v>-1.888920356329621</v>
-      </c>
+        <v>1.307707474268436</v>
+      </c>
+      <c r="C79" t="inlineStr"/>
+      <c r="D79" t="inlineStr"/>
+      <c r="E79" t="inlineStr"/>
+      <c r="F79" t="inlineStr"/>
       <c r="G79" t="inlineStr"/>
       <c r="H79" t="inlineStr"/>
       <c r="I79" t="inlineStr"/>
-      <c r="J79" t="n">
-        <v>-2.876351306287587</v>
-      </c>
+      <c r="J79" t="inlineStr"/>
       <c r="K79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" s="1" t="inlineStr">
         <is>
-          <t>Q to D</t>
-        </is>
-      </c>
-      <c r="B80" t="n">
-        <v>-1.042250049799073</v>
-      </c>
+          <t>C to V</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr"/>
       <c r="C80" t="inlineStr"/>
       <c r="D80" t="inlineStr"/>
       <c r="E80" t="n">
-        <v>-0.6897540732350171</v>
+        <v>-3.206384370288202</v>
       </c>
       <c r="F80" t="inlineStr"/>
       <c r="G80" t="inlineStr"/>
@@ -2486,7 +2458,7 @@
     <row r="81">
       <c r="A81" s="1" t="inlineStr">
         <is>
-          <t>F to P</t>
+          <t>R to F</t>
         </is>
       </c>
       <c r="B81" t="inlineStr"/>
@@ -2494,37 +2466,31 @@
       <c r="D81" t="inlineStr"/>
       <c r="E81" t="inlineStr"/>
       <c r="F81" t="n">
-        <v>-1.982962899156609</v>
+        <v>-2.494653312636166</v>
       </c>
       <c r="G81" t="inlineStr"/>
       <c r="H81" t="inlineStr"/>
       <c r="I81" t="inlineStr"/>
-      <c r="J81" t="inlineStr"/>
+      <c r="J81" t="n">
+        <v>-1.990583297831177</v>
+      </c>
       <c r="K81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" s="1" t="inlineStr">
         <is>
-          <t>E to D</t>
-        </is>
-      </c>
-      <c r="B82" t="n">
-        <v>-0.4225199078514148</v>
-      </c>
-      <c r="C82" t="n">
-        <v>-0.2674458955549505</v>
-      </c>
-      <c r="D82" t="n">
-        <v>-1.966506052238806</v>
-      </c>
+          <t>T to C</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr"/>
+      <c r="C82" t="inlineStr"/>
+      <c r="D82" t="inlineStr"/>
       <c r="E82" t="inlineStr"/>
-      <c r="F82" t="n">
-        <v>-0.3294074970866585</v>
-      </c>
-      <c r="G82" t="n">
-        <v>0.04646614880749206</v>
-      </c>
-      <c r="H82" t="inlineStr"/>
+      <c r="F82" t="inlineStr"/>
+      <c r="G82" t="inlineStr"/>
+      <c r="H82" t="n">
+        <v>-2.772021341363324</v>
+      </c>
       <c r="I82" t="inlineStr"/>
       <c r="J82" t="inlineStr"/>
       <c r="K82" t="inlineStr"/>
@@ -2532,93 +2498,117 @@
     <row r="83">
       <c r="A83" s="1" t="inlineStr">
         <is>
-          <t>A to G</t>
+          <t>Q to S</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>-0.5317275257810317</v>
-      </c>
-      <c r="C83" t="n">
-        <v>-3.202684684370035</v>
-      </c>
+        <v>-1.790193560975912</v>
+      </c>
+      <c r="C83" t="inlineStr"/>
       <c r="D83" t="n">
-        <v>-2.165109501332983</v>
+        <v>-1.879743654261167</v>
       </c>
       <c r="E83" t="inlineStr"/>
-      <c r="F83" t="n">
-        <v>-2.755936204476399</v>
-      </c>
+      <c r="F83" t="inlineStr"/>
       <c r="G83" t="inlineStr"/>
       <c r="H83" t="inlineStr"/>
       <c r="I83" t="inlineStr"/>
       <c r="J83" t="inlineStr"/>
-      <c r="K83" t="n">
-        <v>-2.230254087621095</v>
-      </c>
+      <c r="K83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" s="1" t="inlineStr">
         <is>
-          <t>S to G</t>
+          <t>Q to G</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>-2.867905793283137</v>
+        <v>-1.631396635803113</v>
       </c>
       <c r="C84" t="n">
-        <v>-1.524159150723433</v>
+        <v>-2.019896936152168</v>
       </c>
       <c r="D84" t="n">
-        <v>0.9660662627030125</v>
+        <v>-2.428508034998956</v>
       </c>
       <c r="E84" t="n">
-        <v>-1.706136224905055</v>
+        <v>-2.230292925826905</v>
       </c>
       <c r="F84" t="n">
-        <v>-2.151722908579604</v>
-      </c>
-      <c r="G84" t="inlineStr"/>
+        <v>-2.174714118913573</v>
+      </c>
+      <c r="G84" t="n">
+        <v>-1.427040646908441</v>
+      </c>
       <c r="H84" t="n">
-        <v>-0.946960170181026</v>
+        <v>-1.882813650363043</v>
       </c>
       <c r="I84" t="inlineStr"/>
-      <c r="J84" t="inlineStr"/>
-      <c r="K84" t="inlineStr"/>
+      <c r="J84" t="n">
+        <v>-1.606837129471362</v>
+      </c>
+      <c r="K84" t="n">
+        <v>-1.514233604564605</v>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="1" t="inlineStr">
         <is>
-          <t>C to A</t>
+          <t>W to S</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>1.307707474268436</v>
-      </c>
-      <c r="C85" t="inlineStr"/>
-      <c r="D85" t="inlineStr"/>
-      <c r="E85" t="inlineStr"/>
-      <c r="F85" t="inlineStr"/>
-      <c r="G85" t="inlineStr"/>
-      <c r="H85" t="inlineStr"/>
+        <v>-2.433354501560562</v>
+      </c>
+      <c r="C85" t="n">
+        <v>-2.197809391453416</v>
+      </c>
+      <c r="D85" t="n">
+        <v>-2.688055575218811</v>
+      </c>
+      <c r="E85" t="n">
+        <v>-2.260979225408565</v>
+      </c>
+      <c r="F85" t="n">
+        <v>-3.01459567260336</v>
+      </c>
+      <c r="G85" t="n">
+        <v>-2.354252076144672</v>
+      </c>
+      <c r="H85" t="n">
+        <v>-2.60012179261971</v>
+      </c>
       <c r="I85" t="inlineStr"/>
-      <c r="J85" t="inlineStr"/>
+      <c r="J85" t="n">
+        <v>-2.182769764986223</v>
+      </c>
       <c r="K85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" s="1" t="inlineStr">
         <is>
-          <t>Q to P</t>
+          <t>T to S</t>
         </is>
       </c>
       <c r="B86" t="inlineStr"/>
-      <c r="C86" t="inlineStr"/>
-      <c r="D86" t="inlineStr"/>
+      <c r="C86" t="n">
+        <v>-1.295784631214332</v>
+      </c>
+      <c r="D86" t="n">
+        <v>-0.3115495110783237</v>
+      </c>
       <c r="E86" t="n">
-        <v>0.01996122983687781</v>
-      </c>
-      <c r="F86" t="inlineStr"/>
-      <c r="G86" t="inlineStr"/>
-      <c r="H86" t="inlineStr"/>
+        <v>-0.2967358405509591</v>
+      </c>
+      <c r="F86" t="n">
+        <v>-1.772160073286773</v>
+      </c>
+      <c r="G86" t="n">
+        <v>-2.793307424141744</v>
+      </c>
+      <c r="H86" t="n">
+        <v>-0.6617959991633851</v>
+      </c>
       <c r="I86" t="inlineStr"/>
       <c r="J86" t="inlineStr"/>
       <c r="K86" t="inlineStr"/>
@@ -2626,107 +2616,117 @@
     <row r="87">
       <c r="A87" s="1" t="inlineStr">
         <is>
-          <t>L to E</t>
+          <t>S to C</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>-0.3139181578271339</v>
-      </c>
-      <c r="C87" t="inlineStr"/>
-      <c r="D87" t="inlineStr"/>
-      <c r="E87" t="inlineStr"/>
-      <c r="F87" t="inlineStr"/>
-      <c r="G87" t="inlineStr"/>
+        <v>-1.119477822045281</v>
+      </c>
+      <c r="C87" t="n">
+        <v>-0.5420251763689677</v>
+      </c>
+      <c r="D87" t="n">
+        <v>-0.76889570955057</v>
+      </c>
+      <c r="E87" t="n">
+        <v>-0.9980608897109512</v>
+      </c>
+      <c r="F87" t="n">
+        <v>0.1052649444633963</v>
+      </c>
+      <c r="G87" t="n">
+        <v>-1.420409791970981</v>
+      </c>
       <c r="H87" t="inlineStr"/>
       <c r="I87" t="inlineStr"/>
-      <c r="J87" t="inlineStr"/>
+      <c r="J87" t="n">
+        <v>-1.696480754036708</v>
+      </c>
       <c r="K87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" s="1" t="inlineStr">
         <is>
-          <t>V to T</t>
+          <t>N to M</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>-2.381487207945247</v>
-      </c>
-      <c r="C88" t="inlineStr"/>
-      <c r="D88" t="inlineStr"/>
-      <c r="E88" t="inlineStr"/>
-      <c r="F88" t="inlineStr"/>
+        <v>-1.896177495696552</v>
+      </c>
+      <c r="C88" t="n">
+        <v>-1.862261963638834</v>
+      </c>
+      <c r="D88" t="n">
+        <v>-1.903982009937961</v>
+      </c>
+      <c r="E88" t="n">
+        <v>-2.184650077067929</v>
+      </c>
+      <c r="F88" t="n">
+        <v>-0.854069456964569</v>
+      </c>
       <c r="G88" t="inlineStr"/>
-      <c r="H88" t="n">
-        <v>-1.438918787536255</v>
-      </c>
+      <c r="H88" t="inlineStr"/>
       <c r="I88" t="inlineStr"/>
       <c r="J88" t="n">
-        <v>-1.945923322388674</v>
-      </c>
-      <c r="K88" t="inlineStr"/>
+        <v>-1.864916815978686</v>
+      </c>
+      <c r="K88" t="n">
+        <v>-1.95474476750725</v>
+      </c>
     </row>
     <row r="89">
       <c r="A89" s="1" t="inlineStr">
         <is>
-          <t>M to V</t>
+          <t>Q to A</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>-0.2241391488972727</v>
+        <v>-0.3619759289519581</v>
       </c>
       <c r="C89" t="n">
-        <v>-1.281438780384316</v>
+        <v>0.1069646733456389</v>
       </c>
       <c r="D89" t="n">
-        <v>-2.562784537507083</v>
-      </c>
-      <c r="E89" t="inlineStr"/>
+        <v>-2.660431542968581</v>
+      </c>
+      <c r="E89" t="n">
+        <v>-1.61613884039599</v>
+      </c>
       <c r="F89" t="n">
-        <v>-1.714215125015041</v>
+        <v>0.009813389509508098</v>
       </c>
       <c r="G89" t="n">
-        <v>-1.612589937679346</v>
-      </c>
-      <c r="H89" t="inlineStr"/>
+        <v>-0.626884783722778</v>
+      </c>
+      <c r="H89" t="n">
+        <v>-1.271921085739113</v>
+      </c>
       <c r="I89" t="inlineStr"/>
       <c r="J89" t="n">
-        <v>0.1066627319573099</v>
+        <v>0.763254670072101</v>
       </c>
       <c r="K89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" s="1" t="inlineStr">
         <is>
-          <t>A to V</t>
-        </is>
-      </c>
-      <c r="B90" t="n">
-        <v>-0.8384401961887611</v>
-      </c>
-      <c r="C90" t="n">
-        <v>-0.4625713977352778</v>
-      </c>
+          <t>M to I/L</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr"/>
+      <c r="C90" t="inlineStr"/>
       <c r="D90" t="n">
-        <v>-0.7377364482591892</v>
-      </c>
-      <c r="E90" t="n">
-        <v>-0.2492998169569994</v>
-      </c>
+        <v>-0.08440509815701522</v>
+      </c>
+      <c r="E90" t="inlineStr"/>
       <c r="F90" t="n">
-        <v>-0.7874788780152924</v>
-      </c>
-      <c r="G90" t="n">
-        <v>-1.130231168418733</v>
-      </c>
-      <c r="H90" t="n">
-        <v>-0.4314091091965606</v>
-      </c>
-      <c r="I90" t="n">
-        <v>-1.187371363352375</v>
-      </c>
-      <c r="J90" t="n">
-        <v>-0.8749139941855311</v>
-      </c>
+        <v>0.01961211254722646</v>
+      </c>
+      <c r="G90" t="inlineStr"/>
+      <c r="H90" t="inlineStr"/>
+      <c r="I90" t="inlineStr"/>
+      <c r="J90" t="inlineStr"/>
       <c r="K90" t="inlineStr"/>
     </row>
   </sheetData>
